--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-25T10:48:48.617477+00:00</t>
+          <t>2026-10-25T12:57:17.122484+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40185974249</t>
+          <t>40195065175</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-25T10</t>
+          <t>2026-10-25T12</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/GUaQO2qJyJs</t>
+          <t>https://youtube.com/shorts/em1XeagyUVk</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-25T10/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-25T12/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Find Duplicate Filenames in Python</t>
+          <t>Python: Read CSV and Show Top 5 Rows</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Duplicate filenames clutter your data; this Python method identifies them safely.</t>
+          <t>Stop guessing your data layout. Preview the top five CSV rows now.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13">
@@ -578,7 +578,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>The Mistake</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Find Duplicate Filenames in Python</t>
+          <t>Python: Read CSV and Show Top 5 Rows</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to find duplicate filenames across multiple folders using Python. This safe, read-only script helps you identify naming conflicts without altering your files. Perfect for organizing large data sets.</t>
+          <t>Learn how to safely preview a CSV file in Python using pandas. This short demonstrates reading the top five rows to verify data structure without modifying your source file. Essential for data exploration.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #CodingTips, #DataManagement, #Scripting</t>
+          <t>#python, #pandas, #csv, #datascience</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Duplicate filenames clutter your data; this Python method identifies them safely. Duplicates cause confusion and wasted storage. Use the os module to walk through directories. Build a dictionary mapping names to paths. If a name appears twice, it is a duplicate. Print the results to verify. This method is read-only and safe. It does not modify or delete anything. You can run it on large trees quickly. It helps clean up messy project structures. Subscribe for practical Python tips.</t>
+          <t>Stop guessing your data layout. Preview the top five CSV rows now. Read the first five rows safely. Import pandas, which handles large files efficiently. Load your file using the read_csv function. Then call the head method with five as the argument. This displays the header and first five data entries. It avoids loading the entire dataset into memory. Perfect for quick validation before processing. Your original file remains completely untouched. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,15 +722,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Duplicate filenames clutter your data; this Python method identifies them safely.</t>
+          <t>Stop guessing your data layout. Preview the top five CSV rows now.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>The Mistake</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -743,18 +743,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Find Duplicate Filenames in Python</t>
+          <t>Python: Read CSV and Show Top 5 Rows</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>['no-number', 'no number, date or name - the most reliable single fix']</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-25T12:57:17.122484+00:00</t>
+          <t>2026-10-25T18:53:09.217038+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40195065175</t>
+          <t>40222953107</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-25T12</t>
+          <t>2026-10-25T18</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/em1XeagyUVk</t>
+          <t>https://youtube.com/shorts/gK_8-4wjicM</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-25T12/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-25T18/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Python: Read CSV and Show Top 5 Rows</t>
+          <t>Find Large Files in Python</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stop guessing your data layout. Preview the top five CSV rows now.</t>
+          <t>This Python script lists the largest files in your current directory.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13">
@@ -578,7 +578,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Mistake</t>
+          <t>Unclassified</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Python: Read CSV and Show Top 5 Rows</t>
+          <t>Find Large Files in Python</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to safely preview a CSV file in Python using pandas. This short demonstrates reading the top five rows to verify data structure without modifying your source file. Essential for data exploration.</t>
+          <t>Learn how to use Python's os module to find the largest files in a directory. This safe technique helps you manage disk space without altering your data.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#python, #pandas, #csv, #datascience</t>
+          <t>#Python, #Coding, #DiskSpace, #Programming</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Stop guessing your data layout. Preview the top five CSV rows now. Read the first five rows safely. Import pandas, which handles large files efficiently. Load your file using the read_csv function. Then call the head method with five as the argument. This displays the header and first five data entries. It avoids loading the entire dataset into memory. Perfect for quick validation before processing. Your original file remains completely untouched. Subscribe for practical Python tips.</t>
+          <t>This Python script lists the largest files in your current directory. Python can quickly identify which files consume the most disk space. Start by importing the os module. Iterate through your directory listing. Use os.path.getsize to retrieve each file's size in bytes. Store these values in a list of tuples. Sort the list in descending order. Print the top five results. This helps you locate large files safely. No files are modified during this process. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,15 +722,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Stop guessing your data layout. Preview the top five CSV rows now.</t>
+          <t>This Python script lists the largest files in your current directory.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>The Mistake</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -743,14 +743,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Python: Read CSV and Show Top 5 Rows</t>
+          <t>Find Large Files in Python</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>['no-number', 'no number, date or name - the most reliable single fix']</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-25T18:53:09.217038+00:00</t>
+          <t>2026-10-25T20:46:48.725060+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40222953107</t>
+          <t>40231962112</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-25T18</t>
+          <t>2026-10-25T20</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/gK_8-4wjicM</t>
+          <t>https://youtube.com/shorts/j7Mfk4Hfue8</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-25T18/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-25T20/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Find Large Files in Python</t>
+          <t>Python: Create Strong Random Passwords</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>This Python script lists the largest files in your current directory.</t>
+          <t>You can create strong random passwords on your machine with Python.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13">
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Find Large Files in Python</t>
+          <t>Python: Create Strong Random Passwords</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to use Python's os module to find the largest files in a directory. This safe technique helps you manage disk space without altering your data.</t>
+          <t>Learn how to generate strong, random passwords locally using Python's secrets module. This tutorial demonstrates a secure method to create unique credentials without relying on external services or weak random generators. Follow along to write your own password generator script.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #Coding, #DiskSpace, #Programming</t>
+          <t>#python, #cybersecurity, #coding, #passwordmanagement</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>This Python script lists the largest files in your current directory. Python can quickly identify which files consume the most disk space. Start by importing the os module. Iterate through your directory listing. Use os.path.getsize to retrieve each file's size in bytes. Store these values in a list of tuples. Sort the list in descending order. Print the top five results. This helps you locate large files safely. No files are modified during this process. Subscribe for practical Python tips.</t>
+          <t>You can create strong random passwords on your machine with Python. Import the secrets module to ensure cryptographic randomness. Define a string containing letters, digits, and symbols. Use secrets.choice to select random characters from this pool. Join the selected characters into a single string. Print the result to see your new password. This method keeps your data private and secure. It avoids weak random generators found in older scripts. You control the length and character set easily. Use this script to manage credentials safely. Always store passwords in a dedicated manager. Never write them directly to plain text files. This approach enhances your personal digital security. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,11 +722,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>This Python script lists the largest files in your current directory.</t>
+          <t>You can create strong random passwords on your machine with Python.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Find Large Files in Python</t>
+          <t>Python: Create Strong Random Passwords</t>
         </is>
       </c>
       <c r="C3" t="n">

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-25T20:46:48.725060+00:00</t>
+          <t>2026-10-25T22:43:51.524296+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40231962112</t>
+          <t>40241306836</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-25T20</t>
+          <t>2026-10-25T22</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/j7Mfk4Hfue8</t>
+          <t>https://youtube.com/shorts/a26Cyy6G568</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-25T20/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-25T22/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Python: Create Strong Random Passwords</t>
+          <t>Bulk Rename Files Safely in Python</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>You can create strong random passwords on your machine with Python.</t>
+          <t>Python offers safe ways to batch rename your files.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Python: Create Strong Random Passwords</t>
+          <t>Bulk Rename Files Safely in Python</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to generate strong, random passwords locally using Python's secrets module. This tutorial demonstrates a secure method to create unique credentials without relying on external services or weak random generators. Follow along to write your own password generator script.</t>
+          <t>Learn how to safely rename multiple files using Python. This tutorial covers listing files, checking for conflicts, and using dry-runs to prevent data loss. Perfect for developers and data managers.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#python, #cybersecurity, #coding, #passwordmanagement</t>
+          <t>#Python, #Programming, #FileManagement, #CodingTips</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>You can create strong random passwords on your machine with Python. Import the secrets module to ensure cryptographic randomness. Define a string containing letters, digits, and symbols. Use secrets.choice to select random characters from this pool. Join the selected characters into a single string. Print the result to see your new password. This method keeps your data private and secure. It avoids weak random generators found in older scripts. You control the length and character set easily. Use this script to manage credentials safely. Always store passwords in a dedicated manager. Never write them directly to plain text files. This approach enhances your personal digital security. Subscribe for practical Python tips.</t>
+          <t>Python offers safe ways to batch rename your files. Python offers safe ways to batch rename your files. Avoid data loss when renaming multiple files in Python. Here is a safe Python method for bulk renaming. First, list all target files to verify names. Check for existing conflicts before proceeding. Use a dry-run mode to preview changes. Only execute renaming after confirming accuracy. This prevents accidental overwrites or errors. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,11 +722,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>You can create strong random passwords on your machine with Python.</t>
+          <t>Python offers safe ways to batch rename your files.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Python: Create Strong Random Passwords</t>
+          <t>Bulk Rename Files Safely in Python</t>
         </is>
       </c>
       <c r="C3" t="n">

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-25T22:43:51.524296+00:00</t>
+          <t>2026-10-26T01:28:36.124293+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40241306836</t>
+          <t>40252786793</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-25T22</t>
+          <t>2026-10-26T01</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/a26Cyy6G568</t>
+          <t>https://youtube.com/shorts/g0SYbJzlTKg</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-25T22/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-26T01/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bulk Rename Files Safely in Python</t>
+          <t>Quickly View First 5 CSV Rows</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Python offers safe ways to batch rename your files.</t>
+          <t>Need to check if your CSV file loaded correctly? This quick Python snippet shows you the top five rows instantly.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13">
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bulk Rename Files Safely in Python</t>
+          <t>Quickly View First 5 CSV Rows</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to safely rename multiple files using Python. This tutorial covers listing files, checking for conflicts, and using dry-runs to prevent data loss. Perfect for developers and data managers.</t>
+          <t>Learn how to safely read a CSV file and display the first five rows using Python and Pandas. This simple technique helps verify data structure before processing.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #Programming, #FileManagement, #CodingTips</t>
+          <t>#python, #pandas, #datascience, #codingtips</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Python offers safe ways to batch rename your files. Python offers safe ways to batch rename your files. Avoid data loss when renaming multiple files in Python. Here is a safe Python method for bulk renaming. First, list all target files to verify names. Check for existing conflicts before proceeding. Use a dry-run mode to preview changes. Only execute renaming after confirming accuracy. This prevents accidental overwrites or errors. Subscribe for practical Python tips.</t>
+          <t>Need to check if your CSV file loaded correctly? This quick Python snippet shows you the top five rows instantly. This quick Python snippet shows you the top five rows instantly. First, import the pandas library, which is the standard for data manipulation. Next, call the read_csv function and pass your filename as a string argument. This creates a DataFrame object containing your structured data. Finally, apply the head method with the integer five as its argument. This displays the first five rows in your terminal, allowing you to verify column names and data types. It is a safe, non-destructive way to inspect files without loading excessive memory. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,11 +722,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Python offers safe ways to batch rename your files.</t>
+          <t>Need to check if your CSV file loaded correctly? This quick Python snippet shows you the top five rows instantly.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -743,18 +743,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bulk Rename Files Safely in Python</t>
+          <t>Quickly View First 5 CSV Rows</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>['no-number', 'no number, date or name - the most reliable single fix']</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-26T01:28:36.124293+00:00</t>
+          <t>2026-10-26T02:54:28.258687+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40252786793</t>
+          <t>40260955144</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-26T01</t>
+          <t>2026-10-26T02</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/g0SYbJzlTKg</t>
+          <t>https://youtube.com/shorts/7xNCojLcpB8</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-26T01/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-26T02/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Quickly View First 5 CSV Rows</t>
+          <t>Find Largest Files with Python</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Need to check if your CSV file loaded correctly? This quick Python snippet shows you the top five rows instantly.</t>
+          <t>Stop guessing which files eat your disk space in Python.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13">
@@ -578,7 +578,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>The Mistake</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Quickly View First 5 CSV Rows</t>
+          <t>Find Largest Files with Python</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to safely read a CSV file and display the first five rows using Python and Pandas. This simple technique helps verify data structure before processing.</t>
+          <t>Learn how to find the largest files in a directory using Python. This safe, read-only script helps you identify disk space hogs without modifying any data. Perfect for system maintenance and storage optimization.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#python, #pandas, #datascience, #codingtips</t>
+          <t>#Python, #CodingTips, #DiskSpace, #Programming</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Need to check if your CSV file loaded correctly? This quick Python snippet shows you the top five rows instantly. This quick Python snippet shows you the top five rows instantly. First, import the pandas library, which is the standard for data manipulation. Next, call the read_csv function and pass your filename as a string argument. This creates a DataFrame object containing your structured data. Finally, apply the head method with the integer five as its argument. This displays the first five rows in your terminal, allowing you to verify column names and data types. It is a safe, non-destructive way to inspect files without loading excessive memory. Subscribe for practical Python tips.</t>
+          <t>Stop guessing which files eat your disk space in Python. We will scan your directory to find the largest files. First, import the os and pathlib modules. Use pathlib to walk through your chosen folder. Calculate the size of each file found. Store these sizes in a dictionary. Sort the dictionary by value in descending order. Print the top five largest files. This method is read-only and safe. It helps you identify storage hogs without risk. Try this simple script on your own machine. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,15 +722,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Need to check if your CSV file loaded correctly? This quick Python snippet shows you the top five rows instantly.</t>
+          <t>Stop guessing which files eat your disk space in Python.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>The Mistake</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -743,14 +743,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Quickly View First 5 CSV Rows</t>
+          <t>Find Largest Files with Python</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>['no-number', 'no number, date or name - the most reliable single fix']</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-26T02:54:28.258687+00:00</t>
+          <t>2026-10-26T04:53:00.831094+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40260955144</t>
+          <t>40270976761</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-26T02</t>
+          <t>2026-10-26T04</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/7xNCojLcpB8</t>
+          <t>https://youtube.com/shorts/XHyY0FmgTWg</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-26T02/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-26T04/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Find Largest Files with Python</t>
+          <t>Python Script to Check Disk Usage</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stop guessing which files eat your disk space in Python.</t>
+          <t>Stop guessing which files use storage; let Python find them for you.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13">
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Find Largest Files with Python</t>
+          <t>Python Script to Check Disk Usage</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to find the largest files in a directory using Python. This safe, read-only script helps you identify disk space hogs without modifying any data. Perfect for system maintenance and storage optimization.</t>
+          <t>Learn how to identify which files use the most disk space using Python. This safe script scans directories and lists the largest files without modifying or deleting anything. Perfect for understanding storage usage.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #CodingTips, #DiskSpace, #Programming</t>
+          <t>#Python, #DiskSpace, #CodingTips, #FileManagement</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Stop guessing which files eat your disk space in Python. We will scan your directory to find the largest files. First, import the os and pathlib modules. Use pathlib to walk through your chosen folder. Calculate the size of each file found. Store these sizes in a dictionary. Sort the dictionary by value in descending order. Print the top five largest files. This method is read-only and safe. It helps you identify storage hogs without risk. Try this simple script on your own machine. Subscribe for practical Python tips.</t>
+          <t>Stop guessing which files use storage; let Python find them for you. This Python approach helps you audit disk usage without risk. We use the os module to walk through directories safely. It calculates file sizes in bytes and sorts them by magnitude. No files are modified or deleted during this process. You get a clear list of the largest items. This helps you understand where storage is actually being used. It is a simple, safe way to inspect your data. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,11 +722,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Stop guessing which files eat your disk space in Python.</t>
+          <t>Stop guessing which files use storage; let Python find them for you.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Find Largest Files with Python</t>
+          <t>Python Script to Check Disk Usage</t>
         </is>
       </c>
       <c r="C3" t="n">

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-26T04:53:00.831094+00:00</t>
+          <t>2026-10-26T07:09:56.156646+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40270976761</t>
+          <t>40283478310</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-26T04</t>
+          <t>2026-10-26T07</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/XHyY0FmgTWg</t>
+          <t>https://youtube.com/shorts/F0ASuzqazrU</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-26T04/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-26T07/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Python Script to Check Disk Usage</t>
+          <t>Create Secure Passwords with Python</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stop guessing which files use storage; let Python find them for you.</t>
+          <t>You can create secure random passwords entirely offline using simple Python code.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
@@ -578,7 +578,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Mistake</t>
+          <t>Unclassified</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Python Script to Check Disk Usage</t>
+          <t>Create Secure Passwords with Python</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to identify which files use the most disk space using Python. This safe script scans directories and lists the largest files without modifying or deleting anything. Perfect for understanding storage usage.</t>
+          <t>Learn how to generate strong, random passwords locally using Python's secrets module. This tutorial shows you how to create secure credentials without sending data to external servers. Perfect for improving your password security habits.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #DiskSpace, #CodingTips, #FileManagement</t>
+          <t>#Python, #CyberSecurity, #Programming, #TechTips</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Stop guessing which files use storage; let Python find them for you. This Python approach helps you audit disk usage without risk. We use the os module to walk through directories safely. It calculates file sizes in bytes and sorts them by magnitude. No files are modified or deleted during this process. You get a clear list of the largest items. This helps you understand where storage is actually being used. It is a simple, safe way to inspect your data. Subscribe for practical Python tips.</t>
+          <t>You can create secure random passwords entirely offline using simple Python code. Reusing credentials is risky, but creating unique ones manually is tedious. Python’s secrets module solves this by generating cryptographically secure random values. It ensures unpredictability without relying on external servers or APIs. You can define a character set including letters, numbers, and symbols. Then, use choice to pick random characters from that set. Join them into a string to form your password. This method keeps your data private and secure. It runs entirely on your machine, ensuring no data leaves your device. Try it yourself to improve your digital hygiene. Subscribe for more practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,15 +722,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Stop guessing which files use storage; let Python find them for you.</t>
+          <t>You can create secure random passwords entirely offline using simple Python code.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>The Mistake</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -743,7 +743,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Python Script to Check Disk Usage</t>
+          <t>Create Secure Passwords with Python</t>
         </is>
       </c>
       <c r="C3" t="n">

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-26T07:09:56.156646+00:00</t>
+          <t>2026-10-26T10:59:40.245777+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40283478310</t>
+          <t>40310866313</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-26T07</t>
+          <t>2026-10-26T10</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/F0ASuzqazrU</t>
+          <t>https://youtube.com/shorts/4mJN1Zn4mas</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-26T07/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-26T10/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Create Secure Passwords with Python</t>
+          <t>Organize Downloads View: Extension Sort</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>You can create secure random passwords entirely offline using simple Python code.</t>
+          <t>Sort your downloads by extension using a safe Python preview.</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Create Secure Passwords with Python</t>
+          <t>Organize Downloads View: Extension Sort</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to generate strong, random passwords locally using Python's secrets module. This tutorial shows you how to create secure credentials without sending data to external servers. Perfect for improving your password security habits.</t>
+          <t>Learn how to preview how your downloads folder would look if sorted by file extension using Python. This safe, read-only method helps you plan your file organization without risking data loss. Perfect for developers and data enthusiasts.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #CyberSecurity, #Programming, #TechTips</t>
+          <t>#Python, #FileManagement, #CodingTips, #Productivity</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>You can create secure random passwords entirely offline using simple Python code. Reusing credentials is risky, but creating unique ones manually is tedious. Python’s secrets module solves this by generating cryptographically secure random values. It ensures unpredictability without relying on external servers or APIs. You can define a character set including letters, numbers, and symbols. Then, use choice to pick random characters from that set. Join them into a string to form your password. This method keeps your data private and secure. It runs entirely on your machine, ensuring no data leaves your device. Try it yourself to improve your digital hygiene. Subscribe for more practical Python tips.</t>
+          <t>Sort your downloads by extension using a safe Python preview. This technique groups files by type without moving anything. We use the os module to list directory contents safely. The code filters valid extensions and sorts them alphabetically. You see a clean preview of how organized your data could be. No files are modified or deleted during this process. It is a read-only operation that ensures data safety. Use this to plan your file management strategy effectively. Always verify paths before executing any file operations. This method helps you visualize organization potential. It provides a clear overview of your digital workspace. Check out our channel for more practical Python tips. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>You can create secure random passwords entirely offline using simple Python code.</t>
+          <t>Sort your downloads by extension using a safe Python preview.</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -743,7 +743,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Create Secure Passwords with Python</t>
+          <t>Organize Downloads View: Extension Sort</t>
         </is>
       </c>
       <c r="C3" t="n">

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-26T10:59:40.245777+00:00</t>
+          <t>2026-10-26T15:01:37.604504+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40310866313</t>
+          <t>40344237071</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-26T10</t>
+          <t>2026-10-26T14</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/4mJN1Zn4mas</t>
+          <t>https://youtube.com/shorts/rrfBtCpS_3M</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-26T10/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-26T14/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Organize Downloads View: Extension Sort</t>
+          <t>Python: Find Duplicate File Names</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sort your downloads by extension using a safe Python preview.</t>
+          <t>Stop guessing which files have duplicate names in your system.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13">
@@ -578,7 +578,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>The Mistake</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Organize Downloads View: Extension Sort</t>
+          <t>Python: Find Duplicate File Names</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to preview how your downloads folder would look if sorted by file extension using Python. This safe, read-only method helps you plan your file organization without risking data loss. Perfect for developers and data enthusiasts.</t>
+          <t>Learn how to find duplicate filenames across multiple folders using Python. This safe, read-only script helps you identify naming conflicts without modifying your files. Perfect for organizing projects and cleaning up directories.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #FileManagement, #CodingTips, #Productivity</t>
+          <t>#Python, #CodingTips, #FileManagement, #Productivity</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sort your downloads by extension using a safe Python preview. This technique groups files by type without moving anything. We use the os module to list directory contents safely. The code filters valid extensions and sorts them alphabetically. You see a clean preview of how organized your data could be. No files are modified or deleted during this process. It is a read-only operation that ensures data safety. Use this to plan your file management strategy effectively. Always verify paths before executing any file operations. This method helps you visualize organization potential. It provides a clear overview of your digital workspace. Check out our channel for more practical Python tips. Subscribe for practical Python tips.</t>
+          <t>Stop guessing which files have duplicate names in your system. Python makes finding duplicate filenames across multiple folders easy. We will use the os module to walk through your file tree. First, we collect all file paths into a list. Then, we extract just the filenames. Finally, we use a set to identify names appearing more than once. This method is read-only and safe. It helps you organize your data without deleting anything. You can adapt this script for any directory structure. It runs quickly even with many folders. Use this technique to keep your projects tidy and efficient. Subscribe for more practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,15 +722,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sort your downloads by extension using a safe Python preview.</t>
+          <t>Stop guessing which files have duplicate names in your system.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>The Mistake</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -743,7 +743,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Organize Downloads View: Extension Sort</t>
+          <t>Python: Find Duplicate File Names</t>
         </is>
       </c>
       <c r="C3" t="n">

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-26T15:01:37.604504+00:00</t>
+          <t>2026-10-26T20:53:46.587783+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40344237071</t>
+          <t>40398935358</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-26T14</t>
+          <t>2026-10-26T20</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/rrfBtCpS_3M</t>
+          <t>https://youtube.com/shorts/WlkFnoBq66I</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-26T14/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-26T20/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Python: Find Duplicate File Names</t>
+          <t>Secure Password Generation in Python</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stop guessing which files have duplicate names in your system.</t>
+          <t>Stop using random for passwords; secrets provides true randomness for security.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13">
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Python: Find Duplicate File Names</t>
+          <t>Secure Password Generation in Python</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to find duplicate filenames across multiple folders using Python. This safe, read-only script helps you identify naming conflicts without modifying your files. Perfect for organizing projects and cleaning up directories.</t>
+          <t>Learn how to generate strong, cryptographically secure passwords locally using Python's secrets module. This technique avoids predictable random number generation and keeps your data private.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #CodingTips, #FileManagement, #Productivity</t>
+          <t>#Python, #CyberSecurity, #Programming, #PasswordSecurity</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Stop guessing which files have duplicate names in your system. Python makes finding duplicate filenames across multiple folders easy. We will use the os module to walk through your file tree. First, we collect all file paths into a list. Then, we extract just the filenames. Finally, we use a set to identify names appearing more than once. This method is read-only and safe. It helps you organize your data without deleting anything. You can adapt this script for any directory structure. It runs quickly even with many folders. Use this technique to keep your projects tidy and efficient. Subscribe for more practical Python tips.</t>
+          <t>Stop using random for passwords; secrets provides true randomness for security. Import secrets to access this secure functionality. Define a character set including letters, digits, and symbols. Use secrets.choice to pick each character independently. Join the list into a single string. This method avoids predictable patterns found in the random module. Run this script locally to generate strong passwords. It ensures high entropy for better security. You can adjust the length as needed. This approach keeps your data private. No external servers are involved. The code is simple and effective. Use this technique for local testing. Always store passwords securely. Do not log them to files. This prevents accidental exposure. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,11 +722,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Stop guessing which files have duplicate names in your system.</t>
+          <t>Stop using random for passwords; secrets provides true randomness for security.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Python: Find Duplicate File Names</t>
+          <t>Secure Password Generation in Python</t>
         </is>
       </c>
       <c r="C3" t="n">

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-26T20:53:46.587783+00:00</t>
+          <t>2026-10-26T22:51:41.592513+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40398935358</t>
+          <t>40415181116</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-26T20</t>
+          <t>2026-10-26T22</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/WlkFnoBq66I</t>
+          <t>https://youtube.com/shorts/h8y6q7qijyc</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-26T20/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-26T22/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Secure Password Generation in Python</t>
+          <t>Safe Bulk File Renaming in Python</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stop using random for passwords; secrets provides true randomness for security.</t>
+          <t>You can rename dozens of files in seconds using a simple Python script that prevents data loss.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
@@ -578,7 +578,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Mistake</t>
+          <t>Unclassified</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Secure Password Generation in Python</t>
+          <t>Safe Bulk File Renaming in Python</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to generate strong, cryptographically secure passwords locally using Python's secrets module. This technique avoids predictable random number generation and keeps your data private.</t>
+          <t>Learn how to safely rename multiple files using Python. This tutorial shows a safe approach to batch renaming without risking data loss. Perfect for developers and data managers.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #CyberSecurity, #Programming, #PasswordSecurity</t>
+          <t>#Python, #CodingTips, #FileManagement, #Programming</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Stop using random for passwords; secrets provides true randomness for security. Import secrets to access this secure functionality. Define a character set including letters, digits, and symbols. Use secrets.choice to pick each character independently. Join the list into a single string. This method avoids predictable patterns found in the random module. Run this script locally to generate strong passwords. It ensures high entropy for better security. You can adjust the length as needed. This approach keeps your data private. No external servers are involved. The code is simple and effective. Use this technique for local testing. Always store passwords securely. Do not log them to files. This prevents accidental exposure. Subscribe for practical Python tips.</t>
+          <t>You can rename dozens of files in seconds using a simple Python script that prevents data loss. You can rename dozens of files in seconds using a simple Python script that prevents data loss. Stop renaming files one by one; use Python to handle the bulk process safely and efficiently. Python offers a reliable way to batch rename files without accidentally deleting important data. Here is how to use Python to rename multiple files quickly while keeping your data secure. Always test with a small batch first to ensure your logic works correctly. This method preserves your original data while applying new naming conventions. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,15 +722,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Stop using random for passwords; secrets provides true randomness for security.</t>
+          <t>You can rename dozens of files in seconds using a simple Python script that prevents data loss.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>The Mistake</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -743,7 +743,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Secure Password Generation in Python</t>
+          <t>Safe Bulk File Renaming in Python</t>
         </is>
       </c>
       <c r="C3" t="n">

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-26T22:51:41.592513+00:00</t>
+          <t>2026-10-27T01:06:52.458131+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40415181116</t>
+          <t>40430118507</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-26T22</t>
+          <t>2026-10-27T01</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/h8y6q7qijyc</t>
+          <t>https://youtube.com/shorts/QxFnhxbA-HE</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-26T22/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-27T01/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Safe Bulk File Renaming in Python</t>
+          <t>Rename 1000 Files Safely with Python in 30 Seconds</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>You can rename dozens of files in seconds using a simple Python script that prevents data loss.</t>
+          <t>You can rename many files safely using a simple Python loop.</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Safe Bulk File Renaming in Python</t>
+          <t>Rename 1000 Files Safely with Python in 30 Seconds</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to safely rename multiple files using Python. This tutorial shows a safe approach to batch renaming without risking data loss. Perfect for developers and data managers.</t>
+          <t>Learn how to safely rename multiple files using Python. This tutorial covers using os.rename and checking for existing files to prevent data loss. Perfect for beginners and intermediate users.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #CodingTips, #FileManagement, #Programming</t>
+          <t>#Python, #CodingTips, #Productivity, #Scripting</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>You can rename dozens of files in seconds using a simple Python script that prevents data loss. You can rename dozens of files in seconds using a simple Python script that prevents data loss. Stop renaming files one by one; use Python to handle the bulk process safely and efficiently. Python offers a reliable way to batch rename files without accidentally deleting important data. Here is how to use Python to rename multiple files quickly while keeping your data secure. Always test with a small batch first to ensure your logic works correctly. This method preserves your original data while applying new naming conventions. Subscribe for practical Python tips.</t>
+          <t>You can rename many files safely using a simple Python loop. You can rename many files safely using a simple Python loop. First, list your directory to see current names. Then, use the os.rename function to change each name. Always check if the new name already exists to prevent overwriting. This method ensures you never lose data during the process. It is fast, reliable, and completely safe for your files. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>You can rename dozens of files in seconds using a simple Python script that prevents data loss.</t>
+          <t>You can rename many files safely using a simple Python loop.</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -743,16 +743,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Safe Bulk File Renaming in Python</t>
+          <t>Rename 1000 Files Safely with Python in 30 Seconds</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>['no-number', 'no number, date or name - the most reliable single fix']</t>
+          <t>['mobile', 'a mobile feed shows about "Rename 1000 Files Safely with Python in..." - check the subject survives']</t>
         </is>
       </c>
     </row>

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-27T01:06:52.458131+00:00</t>
+          <t>2026-10-27T02:49:55.457072+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40430118507</t>
+          <t>40440393963</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-27T01</t>
+          <t>2026-10-27T02</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/QxFnhxbA-HE</t>
+          <t>https://youtube.com/shorts/kl29aghs34s</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-27T01/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-27T02/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rename 1000 Files Safely with Python in 30 Seconds</t>
+          <t>Python Script to Tally File Types</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>You can rename many files safely using a simple Python loop.</t>
+          <t>You can count file extensions in any folder using just two lines of Python code.</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rename 1000 Files Safely with Python in 30 Seconds</t>
+          <t>Python Script to Tally File Types</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to safely rename multiple files using Python. This tutorial covers using os.rename and checking for existing files to prevent data loss. Perfect for beginners and intermediate users.</t>
+          <t>Learn how to count file types in a folder using Python's os module and collections.Counter. This safe, read-only script helps you understand your directory structure without modifying any files.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #CodingTips, #Productivity, #Scripting</t>
+          <t>#Python, #CodingTips, #FileManagement, #Programming</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>You can rename many files safely using a simple Python loop. You can rename many files safely using a simple Python loop. First, list your directory to see current names. Then, use the os.rename function to change each name. Always check if the new name already exists to prevent overwriting. This method ensures you never lose data during the process. It is fast, reliable, and completely safe for your files. Subscribe for practical Python tips.</t>
+          <t>You can count file extensions in any folder using just two lines of Python code. Import os and Counter from collections. Use os.walk to traverse the directory tree safely. Extract the file extension from each filename. Update the Counter object with these extensions. Finally, print the most common types. This script only reads metadata, so it never modifies your files. It is perfect for quick directory audits. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>You can rename many files safely using a simple Python loop.</t>
+          <t>You can count file extensions in any folder using just two lines of Python code.</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -743,16 +743,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rename 1000 Files Safely with Python in 30 Seconds</t>
+          <t>Python Script to Tally File Types</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>['mobile', 'a mobile feed shows about "Rename 1000 Files Safely with Python in..." - check the subject survives']</t>
+          <t>['no-number', 'no number, date or name - the most reliable single fix']</t>
         </is>
       </c>
     </row>

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-27T02:49:55.457072+00:00</t>
+          <t>2026-10-27T04:52:26.235506+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40440393963</t>
+          <t>40451652890</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-27T02</t>
+          <t>2026-10-27T04</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/kl29aghs34s</t>
+          <t>https://youtube.com/shorts/FyKM4uf3fGs</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-27T02/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-27T04/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Python Script to Tally File Types</t>
+          <t>Find Largest Files With Python</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>You can count file extensions in any folder using just two lines of Python code.</t>
+          <t>Stop guessing which files are big; use Python to verify their sizes.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
@@ -578,7 +578,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>The Mistake</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Python Script to Tally File Types</t>
+          <t>Find Largest Files With Python</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to count file types in a folder using Python's os module and collections.Counter. This safe, read-only script helps you understand your directory structure without modifying any files.</t>
+          <t>Learn how to use Python to identify the largest files on your system safely. This read-only script helps you audit disk usage without modifying data.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #CodingTips, #FileManagement, #Programming</t>
+          <t>#Python, #Coding, #Productivity, #TechTips</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>You can count file extensions in any folder using just two lines of Python code. Import os and Counter from collections. Use os.walk to traverse the directory tree safely. Extract the file extension from each filename. Update the Counter object with these extensions. Finally, print the most common types. This script only reads metadata, so it never modifies your files. It is perfect for quick directory audits. Subscribe for practical Python tips.</t>
+          <t>Stop guessing which files are big; use Python to verify their sizes. We will use the os module to walk through your directory tree. This script calculates file sizes safely without altering any data. It sorts results by size, showing the biggest files first. You can easily identify storage hogs in seconds. This approach is read-only, ensuring your files remain untouched. It works on any operating system with standard Python libraries. No external dependencies are required for this basic audit. You gain clarity on where your disk space goes. Use this to plan your storage cleanup effectively. It is a fundamental skill for developers. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,15 +722,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>You can count file extensions in any folder using just two lines of Python code.</t>
+          <t>Stop guessing which files are big; use Python to verify their sizes.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>The Mistake</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -743,7 +743,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Python Script to Tally File Types</t>
+          <t>Find Largest Files With Python</t>
         </is>
       </c>
       <c r="C3" t="n">

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-27T04:52:26.235506+00:00</t>
+          <t>2026-10-27T07:04:57.504499+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40451652890</t>
+          <t>40464407083</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-27T04</t>
+          <t>2026-10-27T07</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/FyKM4uf3fGs</t>
+          <t>https://youtube.com/shorts/AfUxKlGtxl8</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-27T04/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-27T07/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Find Largest Files With Python</t>
+          <t>Safe File Backup in 5 Seconds</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stop guessing which files are big; use Python to verify their sizes.</t>
+          <t>Protect your data by creating timestamped copies easily.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13">
@@ -578,7 +578,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Mistake</t>
+          <t>Unclassified</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Find Largest Files With Python</t>
+          <t>Safe File Backup in 5 Seconds</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to use Python to identify the largest files on your system safely. This read-only script helps you audit disk usage without modifying data.</t>
+          <t>Learn how to create a safe, timestamped backup of a single file using Python. This technique uses shutil.copy2 to preserve metadata while ensuring the original file remains untouched. Perfect for developers looking to add version control to their scripts safely.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #Coding, #Productivity, #TechTips</t>
+          <t>#Python, #Coding, #FileManagement, #ProgrammingTips</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Stop guessing which files are big; use Python to verify their sizes. We will use the os module to walk through your directory tree. This script calculates file sizes safely without altering any data. It sorts results by size, showing the biggest files first. You can easily identify storage hogs in seconds. This approach is read-only, ensuring your files remain untouched. It works on any operating system with standard Python libraries. No external dependencies are required for this basic audit. You gain clarity on where your disk space goes. Use this to plan your storage cleanup effectively. It is a fundamental skill for developers. Subscribe for practical Python tips.</t>
+          <t>Protect your data by creating timestamped copies easily. Learn to back up files safely using Python timestamps. Import shutil and datetime. Read the original file path. Generate a unique timestamp string. Combine the path, timestamp, and extension. Use shutil.copy2 to create the backup. This preserves metadata and avoids modifying the original file. Always verify the destination directory exists first. This method ensures you keep a safe, versioned copy. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,15 +722,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Stop guessing which files are big; use Python to verify their sizes.</t>
+          <t>Protect your data by creating timestamped copies easily.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>The Mistake</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -743,18 +743,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Find Largest Files With Python</t>
+          <t>Safe File Backup in 5 Seconds</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>['no-number', 'no number, date or name - the most reliable single fix']</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-27T07:04:57.504499+00:00</t>
+          <t>2026-10-27T09:04:32.941010+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40464407083</t>
+          <t>40476843446</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-27T07</t>
+          <t>2026-10-27T09</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/AfUxKlGtxl8</t>
+          <t>https://youtube.com/shorts/M0URYusMgU4</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-27T07/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-27T09/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Safe File Backup in 5 Seconds</t>
+          <t>Create Timestamped Backups in Python</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Protect your data by creating timestamped copies easily.</t>
+          <t>Protect your data by creating timestamped copies in Python.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Safe File Backup in 5 Seconds</t>
+          <t>Create Timestamped Backups in Python</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to create a safe, timestamped backup of a single file using Python. This technique uses shutil.copy2 to preserve metadata while ensuring the original file remains untouched. Perfect for developers looking to add version control to their scripts safely.</t>
+          <t>Learn how to create a timestamped backup copy of a single file using Python. This tutorial shows a safe method using shutil and datetime without modifying the original file.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #Coding, #FileManagement, #ProgrammingTips</t>
+          <t>#python, #coding, #backup, #programming</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Protect your data by creating timestamped copies easily. Learn to back up files safely using Python timestamps. Import shutil and datetime. Read the original file path. Generate a unique timestamp string. Combine the path, timestamp, and extension. Use shutil.copy2 to create the backup. This preserves metadata and avoids modifying the original file. Always verify the destination directory exists first. This method ensures you keep a safe, versioned copy. Subscribe for practical Python tips.</t>
+          <t>Protect your data by creating timestamped copies in Python. We use shutil.copy2 to preserve metadata. The datetime module formats the current time. We append this string to the file name. This creates a unique copy every time. No original data is ever modified. Just run the script before editing. It ensures you always have a previous version. This method is fast and reliable for scripts. Your files stay exactly where they are. The backup sits right next to the original. It is simple, safe, and effective for daily use. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,11 +722,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Protect your data by creating timestamped copies easily.</t>
+          <t>Protect your data by creating timestamped copies in Python.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -743,14 +743,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Safe File Backup in 5 Seconds</t>
+          <t>Create Timestamped Backups in Python</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>['no-number', 'no number, date or name - the most reliable single fix']</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-27T09:04:32.941010+00:00</t>
+          <t>2026-10-27T10:57:09.539902+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40476843446</t>
+          <t>40491638625</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-27T09</t>
+          <t>2026-10-27T10</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/M0URYusMgU4</t>
+          <t>https://youtube.com/shorts/gByA0cMnuAA</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-27T09/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-27T10/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Create Timestamped Backups in Python</t>
+          <t>Rename 1,000 Files Safely With Python in 30 Seconds</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Protect your data by creating timestamped copies in Python.</t>
+          <t>Stop renaming files one by one in your file manager.</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>The Mistake</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Create Timestamped Backups in Python</t>
+          <t>Rename 1,000 Files Safely With Python in 30 Seconds</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to create a timestamped backup copy of a single file using Python. This tutorial shows a safe method using shutil and datetime without modifying the original file.</t>
+          <t>Learn how to rename multiple files safely using Python. This tutorial covers safe batch renaming techniques, dry runs, and metadata updates without modifying file contents. Perfect for developers and data managers looking to automate file organization tasks securely.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#python, #coding, #backup, #programming</t>
+          <t>#Python, #Programming, #Automation, #FileManagement</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Protect your data by creating timestamped copies in Python. We use shutil.copy2 to preserve metadata. The datetime module formats the current time. We append this string to the file name. This creates a unique copy every time. No original data is ever modified. Just run the script before editing. It ensures you always have a previous version. This method is fast and reliable for scripts. Your files stay exactly where they are. The backup sits right next to the original. It is simple, safe, and effective for daily use. Subscribe for practical Python tips.</t>
+          <t>Stop renaming files one by one in your file manager. You can rename thousands of files safely using a simple script. First, list your files. Then, apply a consistent naming pattern. Use a dry run flag to preview changes before committing. This ensures no accidental overwrites occur. The script only updates metadata, never file contents. It is fast, reliable, and easy to debug. You maintain full control over the process. No data is lost during the operation. This technique saves hours of manual work. It works on any operating system. Keep your backups current before running any script. This method is safe for professional use. Subscribe for practical Python tips that save you time every day.</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Protect your data by creating timestamped copies in Python.</t>
+          <t>Stop renaming files one by one in your file manager.</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -730,7 +730,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>The Mistake</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -743,16 +743,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Create Timestamped Backups in Python</t>
+          <t>Rename 1,000 Files Safely With Python in 30 Seconds</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>['no-number', 'no number, date or name - the most reliable single fix']</t>
+          <t>['mobile', 'a mobile feed shows about "Rename 1,000 Files Safely With Python..." - check the subject survives']</t>
         </is>
       </c>
     </row>

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-27T10:57:09.539902+00:00</t>
+          <t>2026-10-27T13:05:20.621633+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40491638625</t>
+          <t>40508286407</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-27T10</t>
+          <t>2026-10-27T13</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/gByA0cMnuAA</t>
+          <t>https://youtube.com/shorts/a8VwGlrTtzc</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-27T10/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-27T13/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rename 1,000 Files Safely With Python in 30 Seconds</t>
+          <t>Build a Folder Inventory CSV in 60 Seconds</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stop renaming files one by one in your file manager.</t>
+          <t>Need to audit your project files? This script builds a complete inventory for you.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13">
@@ -578,7 +578,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Mistake</t>
+          <t>Unclassified</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rename 1,000 Files Safely With Python in 30 Seconds</t>
+          <t>Build a Folder Inventory CSV in 60 Seconds</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to rename multiple files safely using Python. This tutorial covers safe batch renaming techniques, dry runs, and metadata updates without modifying file contents. Perfect for developers and data managers looking to automate file organization tasks securely.</t>
+          <t>Learn how to create a simple folder inventory using Python. This script uses os.walk to traverse directories and csv module to export file names and sizes to a CSV file. Perfect for project audits and asset management. Safe, read-only operation.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #Programming, #Automation, #FileManagement</t>
+          <t>#python, #coding, #automation, #csv</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Stop renaming files one by one in your file manager. You can rename thousands of files safely using a simple script. First, list your files. Then, apply a consistent naming pattern. Use a dry run flag to preview changes before committing. This ensures no accidental overwrites occur. The script only updates metadata, never file contents. It is fast, reliable, and easy to debug. You maintain full control over the process. No data is lost during the operation. This technique saves hours of manual work. It works on any operating system. Keep your backups current before running any script. This method is safe for professional use. Subscribe for practical Python tips that save you time every day.</t>
+          <t>Need to audit your project files? This script builds a complete inventory for you. Import the os and csv modules to handle directories and file writing. Define a target directory path where your files are located. Use os.walk to recursively traverse the directory tree. Iterate through each folder and file found. Write the relative path and file size to a CSV file. This creates a clean, organized inventory. It helps you track assets without manual effort. No data is modified, only read. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,15 +722,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Stop renaming files one by one in your file manager.</t>
+          <t>Need to audit your project files? This script builds a complete inventory for you.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>The Mistake</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -743,16 +743,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rename 1,000 Files Safely With Python in 30 Seconds</t>
+          <t>Build a Folder Inventory CSV in 60 Seconds</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>['mobile', 'a mobile feed shows about "Rename 1,000 Files Safely With Python..." - check the subject survives']</t>
+          <t>['mobile', 'a mobile feed shows about "Build a Folder Inventory CSV in 60..." - check the subject survives']</t>
         </is>
       </c>
     </row>

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-27T13:05:20.621633+00:00</t>
+          <t>2026-10-27T15:04:43.412420+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40508286407</t>
+          <t>40526564287</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-27T13</t>
+          <t>2026-10-27T15</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/a8VwGlrTtzc</t>
+          <t>https://youtube.com/shorts/378tAgzO4KE</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-27T13/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-27T15/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Build a Folder Inventory CSV in 60 Seconds</t>
+          <t>Count File Types with Python</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Need to audit your project files? This script builds a complete inventory for you.</t>
+          <t>Master this Python snippet to count file types in your current folder.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13">
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Build a Folder Inventory CSV in 60 Seconds</t>
+          <t>Count File Types with Python</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to create a simple folder inventory using Python. This script uses os.walk to traverse directories and csv module to export file names and sizes to a CSV file. Perfect for project audits and asset management. Safe, read-only operation.</t>
+          <t>Learn how to count file types in a folder using Python. This safe script uses os.listdir to read file names and tally extensions without modifying any data. Perfect for organizing files or analyzing directory contents.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#python, #coding, #automation, #csv</t>
+          <t>#Python, #Coding, #Scripting, #FileManagement</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Need to audit your project files? This script builds a complete inventory for you. Import the os and csv modules to handle directories and file writing. Define a target directory path where your files are located. Use os.walk to recursively traverse the directory tree. Iterate through each folder and file found. Write the relative path and file size to a CSV file. This creates a clean, organized inventory. It helps you track assets without manual effort. No data is modified, only read. Subscribe for practical Python tips.</t>
+          <t>Master this Python snippet to count file types in your current folder. First, import the os module to interact with your file system. Next, list all files in the target directory using os.listdir. Then, split each filename to extract the extension. Store these extensions in a dictionary to track their counts. Finally, print the results to see which file types appear most often. This method only reads file names, ensuring your data remains completely safe. No files are deleted or modified during this process. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,11 +722,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Need to audit your project files? This script builds a complete inventory for you.</t>
+          <t>Master this Python snippet to count file types in your current folder.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -743,16 +743,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Build a Folder Inventory CSV in 60 Seconds</t>
+          <t>Count File Types with Python</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>['mobile', 'a mobile feed shows about "Build a Folder Inventory CSV in 60..." - check the subject survives']</t>
+          <t>['no-number', 'no number, date or name - the most reliable single fix']</t>
         </is>
       </c>
     </row>

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-27T15:04:43.412420+00:00</t>
+          <t>2026-10-27T20:53:57.789161+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40526564287</t>
+          <t>40581332530</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-27T15</t>
+          <t>2026-10-27T20</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/378tAgzO4KE</t>
+          <t>https://youtube.com/shorts/ifXjxohIFnQ</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-27T15/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-27T20/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Count File Types with Python</t>
+          <t>Rename Files Safely With Python</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Master this Python snippet to count file types in your current folder.</t>
+          <t>Stop renaming files one by one in your file explorer.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
@@ -578,7 +578,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>The Mistake</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Count File Types with Python</t>
+          <t>Rename Files Safely With Python</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to count file types in a folder using Python. This safe script uses os.listdir to read file names and tally extensions without modifying any data. Perfect for organizing files or analyzing directory contents.</t>
+          <t>Learn how to safely rename multiple files using Python. This tutorial covers safe string manipulation and existence checks to prevent data loss. Perfect for beginners looking to automate file management tasks securely.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #Coding, #Scripting, #FileManagement</t>
+          <t>#python, #programming, #coding, #productivity</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Master this Python snippet to count file types in your current folder. First, import the os module to interact with your file system. Next, list all files in the target directory using os.listdir. Then, split each filename to extract the extension. Store these extensions in a dictionary to track their counts. Finally, print the results to see which file types appear most often. This method only reads file names, ensuring your data remains completely safe. No files are deleted or modified during this process. Subscribe for practical Python tips.</t>
+          <t>Stop renaming files one by one in your file explorer. Python offers a safe way to rename multiple files at once. This script iterates through a directory list. It constructs new names using simple string logic. Crucially, it checks if the target file already exists. This prevents accidental overwriting of existing data. You can review the proposed changes before execution. This dry-run approach ensures safety and accuracy. It gives you full control over the process. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,15 +722,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Master this Python snippet to count file types in your current folder.</t>
+          <t>Stop renaming files one by one in your file explorer.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>The Mistake</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -743,7 +743,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Count File Types with Python</t>
+          <t>Rename Files Safely With Python</t>
         </is>
       </c>
       <c r="C3" t="n">

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-27T20:53:57.789161+00:00</t>
+          <t>2026-10-27T22:51:42.517584+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40581332530</t>
+          <t>40597512295</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-27T20</t>
+          <t>2026-10-27T22</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/ifXjxohIFnQ</t>
+          <t>https://youtube.com/shorts/7zLuN-zZIhg</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-27T20/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-27T22/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rename Files Safely With Python</t>
+          <t>Find Big Files Instantly With Python</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stop renaming files one by one in your file explorer.</t>
+          <t>Learn how to scan your directory and find the biggest files without installing software.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13">
@@ -578,7 +578,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Mistake</t>
+          <t>The Impossible Claim</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rename Files Safely With Python</t>
+          <t>Find Big Files Instantly With Python</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to safely rename multiple files using Python. This tutorial covers safe string manipulation and existence checks to prevent data loss. Perfect for beginners looking to automate file management tasks securely.</t>
+          <t>Learn how to identify the largest files in any directory using Python. This tutorial shows you how to use the os module to scan folders, calculate file sizes, and sort them to find disk space hogs. It is a safe, read-only method that helps you manage your storage without third-party tools. Perfect for developers and tech enthusiasts looking to optimize their local drives.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#python, #programming, #coding, #productivity</t>
+          <t>#Python, #CodingTips, #DiskSpace, #Productivity</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Stop renaming files one by one in your file explorer. Python offers a safe way to rename multiple files at once. This script iterates through a directory list. It constructs new names using simple string logic. Crucially, it checks if the target file already exists. This prevents accidental overwriting of existing data. You can review the proposed changes before execution. This dry-run approach ensures safety and accuracy. It gives you full control over the process. Subscribe for practical Python tips.</t>
+          <t>Learn how to scan your directory and find the biggest files without installing software. Open your editor and import the os module. Create a list to store file paths and their sizes. Loop through your target directory recursively. Use os.path.getsize to measure each file in bytes. Add these pairs to your list. Sort the list in descending order based on size. Print the top five entries to your console. This safe method reads metadata only. It never modifies or deletes your data. You instantly identify heavy files. This helps you manage storage efficiently. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,15 +722,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Stop renaming files one by one in your file explorer.</t>
+          <t>Learn how to scan your directory and find the biggest files without installing software.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>The Mistake</t>
+          <t>The Impossible Claim</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -743,7 +743,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rename Files Safely With Python</t>
+          <t>Find Big Files Instantly With Python</t>
         </is>
       </c>
       <c r="C3" t="n">

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-27T22:51:42.517584+00:00</t>
+          <t>2026-10-28T01:17:08.705898+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40597512295</t>
+          <t>40613688531</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-27T22</t>
+          <t>2026-10-28T01</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/7zLuN-zZIhg</t>
+          <t>https://youtube.com/shorts/yi1AYyCmGMQ</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-27T22/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-28T01/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Find Big Files Instantly With Python</t>
+          <t>Locate Big Files with Python</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Learn how to scan your directory and find the biggest files without installing software.</t>
+          <t>Stop guessing which files take up space; measure them accurately with Python.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
@@ -578,7 +578,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Impossible Claim</t>
+          <t>The Mistake</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Find Big Files Instantly With Python</t>
+          <t>Locate Big Files with Python</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to identify the largest files in any directory using Python. This tutorial shows you how to use the os module to scan folders, calculate file sizes, and sort them to find disk space hogs. It is a safe, read-only method that helps you manage your storage without third-party tools. Perfect for developers and tech enthusiasts looking to optimize their local drives.</t>
+          <t>Learn how to find the largest files in a directory using Python's os module. This read-only script helps you monitor disk usage without modifying any data.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #CodingTips, #DiskSpace, #Productivity</t>
+          <t>#Python, #CodingTips, #Productivity, #Programming</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Learn how to scan your directory and find the biggest files without installing software. Open your editor and import the os module. Create a list to store file paths and their sizes. Loop through your target directory recursively. Use os.path.getsize to measure each file in bytes. Add these pairs to your list. Sort the list in descending order based on size. Print the top five entries to your console. This safe method reads metadata only. It never modifies or deletes your data. You instantly identify heavy files. This helps you manage storage efficiently. Subscribe for practical Python tips.</t>
+          <t>Stop guessing which files take up space; measure them accurately with Python. Import the os module to access file system operations. List all items in the current directory using os.listdir. Filter for files only, skipping folders entirely. Get the size of each file using os.path.getsize. Store these values in a list of tuples. Sort the list in descending order to find the largest files. Print the top five results to your console. This helps identify unexpected heavy assets. Always check permissions before scanning sensitive folders. This method is safe and read-only. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,15 +722,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Learn how to scan your directory and find the biggest files without installing software.</t>
+          <t>Stop guessing which files take up space; measure them accurately with Python.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>The Impossible Claim</t>
+          <t>The Mistake</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -743,7 +743,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Find Big Files Instantly With Python</t>
+          <t>Locate Big Files with Python</t>
         </is>
       </c>
       <c r="C3" t="n">

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-28T01:17:08.705898+00:00</t>
+          <t>2026-10-28T03:01:40.400339+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40613688531</t>
+          <t>40623875271</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-28T01</t>
+          <t>2026-10-28T02</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/yi1AYyCmGMQ</t>
+          <t>https://youtube.com/shorts/quSoJeOiBPY</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-28T01/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-28T02/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Locate Big Files with Python</t>
+          <t>Python: Find Largest Files</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stop guessing which files take up space; measure them accurately with Python.</t>
+          <t>You can find disk space hogs using a simple Python script.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
@@ -578,7 +578,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Mistake</t>
+          <t>Unclassified</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Locate Big Files with Python</t>
+          <t>Python: Find Largest Files</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to find the largest files in a directory using Python's os module. This read-only script helps you monitor disk usage without modifying any data.</t>
+          <t>Learn how to safely identify the largest files in a directory using Python. This script uses the os module to read file sizes and sort them without modifying any data. Perfect for cleaning up disk space.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #CodingTips, #Productivity, #Programming</t>
+          <t>#Python, #Coding, #Productivity, #TechTips</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Stop guessing which files take up space; measure them accurately with Python. Import the os module to access file system operations. List all items in the current directory using os.listdir. Filter for files only, skipping folders entirely. Get the size of each file using os.path.getsize. Store these values in a list of tuples. Sort the list in descending order to find the largest files. Print the top five results to your console. This helps identify unexpected heavy assets. Always check permissions before scanning sensitive folders. This method is safe and read-only. Subscribe for practical Python tips.</t>
+          <t>You can find disk space hogs using a simple Python script. First, import the os module. Create an empty list to store results. Loop through every file in your target path. Get each file size using os.path.getsize. Append the name and size to your list. Sort the list by size in descending order. Print the top ten entries to your console. This reveals exactly which files consume the most space. It is a read-only inspection method. No data is altered or deleted during this process. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,15 +722,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Stop guessing which files take up space; measure them accurately with Python.</t>
+          <t>You can find disk space hogs using a simple Python script.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>The Mistake</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -743,7 +743,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Locate Big Files with Python</t>
+          <t>Python: Find Largest Files</t>
         </is>
       </c>
       <c r="C3" t="n">

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-28T03:01:40.400339+00:00</t>
+          <t>2026-10-28T05:02:04.703260+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40623875271</t>
+          <t>40635146306</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-28T02</t>
+          <t>2026-10-28T04</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/quSoJeOiBPY</t>
+          <t>https://youtube.com/shorts/poUOdiwOQVU</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-28T02/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-28T04/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Python: Find Largest Files</t>
+          <t>Read CSV &amp; Show Top 5 Rows in Python</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>You can find disk space hogs using a simple Python script.</t>
+          <t>You can preview any CSV file’s first five rows instantly using Python’s built-in library.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Python: Find Largest Files</t>
+          <t>Read CSV &amp; Show Top 5 Rows in Python</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to safely identify the largest files in a directory using Python. This script uses the os module to read file sizes and sort them without modifying any data. Perfect for cleaning up disk space.</t>
+          <t>Learn how to read a CSV file and display the top five rows using Python's pandas library. This quick tutorial shows you how to inspect data efficiently without loading the entire file into memory. Perfect for beginners and data analysts looking to streamline their workflow.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #Coding, #Productivity, #TechTips</t>
+          <t>#python, #pandas, #datascience, #coding</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>You can find disk space hogs using a simple Python script. First, import the os module. Create an empty list to store results. Loop through every file in your target path. Get each file size using os.path.getsize. Append the name and size to your list. Sort the list by size in descending order. Print the top ten entries to your console. This reveals exactly which files consume the most space. It is a read-only inspection method. No data is altered or deleted during this process. Subscribe for practical Python tips.</t>
+          <t>You can preview any CSV file’s first five rows instantly using Python’s built-in library. First, import the pandas library, which handles data tables efficiently. Next, use the read_csv function to load your file into a DataFrame. Then, call the head method with an argument of five. This displays only the first five rows, saving memory. It is perfect for quick inspection. You avoid loading huge datasets into RAM. This keeps your workflow fast and responsive. Always verify your file path before running. This simple technique works across many projects. It helps you understand data structure quickly. Now you know how to peek at your data safely. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,11 +722,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>You can find disk space hogs using a simple Python script.</t>
+          <t>You can preview any CSV file’s first five rows instantly using Python’s built-in library.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -743,18 +743,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Python: Find Largest Files</t>
+          <t>Read CSV &amp; Show Top 5 Rows in Python</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>['no-number', 'no number, date or name - the most reliable single fix']</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-28T05:02:04.703260+00:00</t>
+          <t>2026-10-28T07:16:20.064930+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40635146306</t>
+          <t>40648424270</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-28T04</t>
+          <t>2026-10-28T07</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/poUOdiwOQVU</t>
+          <t>https://youtube.com/shorts/Krdzwsk7sVQ</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-28T04/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-28T07/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Read CSV &amp; Show Top 5 Rows in Python</t>
+          <t>Python: List Folder Contents to CSV</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>You can preview any CSV file’s first five rows instantly using Python’s built-in library.</t>
+          <t>Stop manually listing files; Python can save your folder structure to CSV quickly.</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>The Mistake</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Read CSV &amp; Show Top 5 Rows in Python</t>
+          <t>Python: List Folder Contents to CSV</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to read a CSV file and display the top five rows using Python's pandas library. This quick tutorial shows you how to inspect data efficiently without loading the entire file into memory. Perfect for beginners and data analysts looking to streamline their workflow.</t>
+          <t>Learn how to create a simple folder inventory as a CSV file using Python. This safe technique lists directory contents without modifying any files. Perfect for quick file tracking and organization.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#python, #pandas, #datascience, #coding</t>
+          <t>#Python, #CodingTips, #CSV, #Productivity</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>You can preview any CSV file’s first five rows instantly using Python’s built-in library. First, import the pandas library, which handles data tables efficiently. Next, use the read_csv function to load your file into a DataFrame. Then, call the head method with an argument of five. This displays only the first five rows, saving memory. It is perfect for quick inspection. You avoid loading huge datasets into RAM. This keeps your workflow fast and responsive. Always verify your file path before running. This simple technique works across many projects. It helps you understand data structure quickly. Now you know how to peek at your data safely. Subscribe for practical Python tips.</t>
+          <t>Stop manually listing files; Python can save your folder structure to CSV quickly. Stop manually listing files; Python can save your folder structure to CSV quickly. Import os and csv modules. Create a list for file entries. Loop through directory items using os.listdir. Append each name to the list. Open a CSV file in write mode. Create a writer object. Write each filename to the file. Close the file when finished. Your inventory is ready. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>You can preview any CSV file’s first five rows instantly using Python’s built-in library.</t>
+          <t>Stop manually listing files; Python can save your folder structure to CSV quickly.</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -730,7 +730,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>The Mistake</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -743,14 +743,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Read CSV &amp; Show Top 5 Rows in Python</t>
+          <t>Python: List Folder Contents to CSV</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>['no-number', 'no number, date or name - the most reliable single fix']</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-28T07:16:20.064930+00:00</t>
+          <t>2026-10-28T09:05:42.125667+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40648424270</t>
+          <t>40661070925</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-28T07</t>
+          <t>2026-10-28T09</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/Krdzwsk7sVQ</t>
+          <t>https://youtube.com/shorts/Fx7Avo7n0jQ</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-28T07/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-28T09/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Python: List Folder Contents to CSV</t>
+          <t>Python Script for Disk Space</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stop manually listing files; Python can save your folder structure to CSV quickly.</t>
+          <t>Stop guessing which files are eating your hard drive space.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13">
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Python: List Folder Contents to CSV</t>
+          <t>Python Script for Disk Space</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to create a simple folder inventory as a CSV file using Python. This safe technique lists directory contents without modifying any files. Perfect for quick file tracking and organization.</t>
+          <t>Learn how to use Python to find the largest files on your computer. This script uses os.walk to scan directories and sort files by size, helping you identify what takes up the most disk space safely.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #CodingTips, #CSV, #Productivity</t>
+          <t>#Python, #Coding, #Productivity, #DiskSpace</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Stop manually listing files; Python can save your folder structure to CSV quickly. Stop manually listing files; Python can save your folder structure to CSV quickly. Import os and csv modules. Create a list for file entries. Loop through directory items using os.listdir. Append each name to the list. Open a CSV file in write mode. Create a writer object. Write each filename to the file. Close the file when finished. Your inventory is ready. Subscribe for practical Python tips.</t>
+          <t>Stop guessing which files are eating your hard drive space. Python can quickly identify the largest files on your system. We will use the os module to walk through directories. The code collects file paths and their sizes. Then we sort the list by size in descending order. This shows you the heaviest files first. It helps you locate bulky media or logs. You can then decide what to move or archive. This method is safe and read-only. It does not delete anything automatically. It gives you the data to make informed choices. Try this script to audit your storage today. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,11 +722,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Stop manually listing files; Python can save your folder structure to CSV quickly.</t>
+          <t>Stop guessing which files are eating your hard drive space.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -743,11 +743,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Python: List Folder Contents to CSV</t>
+          <t>Python Script for Disk Space</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-28T09:05:42.125667+00:00</t>
+          <t>2026-10-28T11:01:29.306178+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40661070925</t>
+          <t>40676120888</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-28T09</t>
+          <t>2026-10-28T10</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/Fx7Avo7n0jQ</t>
+          <t>https://youtube.com/shorts/Tz-iK6RLcgg</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-28T09/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-28T10/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Python Script for Disk Space</t>
+          <t>Sort Downloads by Extension Using Python</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stop guessing which files are eating your hard drive space.</t>
+          <t>See how to categorize your download folder using Python code.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13">
@@ -578,7 +578,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Mistake</t>
+          <t>Unclassified</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Python Script for Disk Space</t>
+          <t>Sort Downloads by Extension Using Python</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to use Python to find the largest files on your computer. This script uses os.walk to scan directories and sort files by size, helping you identify what takes up the most disk space safely.</t>
+          <t>Learn how to use Python to organize your downloads folder by file extension. This safe preview method helps you plan your cleanup without moving or modifying any files. Perfect for beginners looking to automate file management.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #Coding, #Productivity, #DiskSpace</t>
+          <t>#python, #coding, #productivity, #filemanagement</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Stop guessing which files are eating your hard drive space. Python can quickly identify the largest files on your system. We will use the os module to walk through directories. The code collects file paths and their sizes. Then we sort the list by size in descending order. This shows you the heaviest files first. It helps you locate bulky media or logs. You can then decide what to move or archive. This method is safe and read-only. It does not delete anything automatically. It gives you the data to make informed choices. Try this script to audit your storage today. Subscribe for practical Python tips.</t>
+          <t>See how to categorize your download folder using Python code. Python can sort your downloads folder by file extension safely. This script scans your directory and groups files by type. It uses pathlib to read extensions without moving anything. You can preview the structure before committing changes. This ensures no data is lost or modified accidentally. It is a safe way to plan your cleanup. Try it in a test folder first. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,15 +722,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Stop guessing which files are eating your hard drive space.</t>
+          <t>See how to categorize your download folder using Python code.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>The Mistake</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -743,7 +743,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Python Script for Disk Space</t>
+          <t>Sort Downloads by Extension Using Python</t>
         </is>
       </c>
       <c r="C3" t="n">

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-28T11:01:29.306178+00:00</t>
+          <t>2026-10-28T13:14:18.651119+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40676120888</t>
+          <t>40693885601</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-28T10</t>
+          <t>2026-10-28T13</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/Tz-iK6RLcgg</t>
+          <t>https://youtube.com/shorts/rZl3jjL3zKk</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-28T10/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-28T13/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sort Downloads by Extension Using Python</t>
+          <t>Python: Find Large Files Fast</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>See how to categorize your download folder using Python code.</t>
+          <t>Stop guessing which files take up space; let Python measure them for you.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13">
@@ -578,7 +578,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>The Mistake</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sort Downloads by Extension Using Python</t>
+          <t>Python: Find Large Files Fast</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to use Python to organize your downloads folder by file extension. This safe preview method helps you plan your cleanup without moving or modifying any files. Perfect for beginners looking to automate file management.</t>
+          <t>Learn how to find the largest files on your system using Python's os module. This read-only script walks through directories and sorts files by size, helping you manage disk space safely.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#python, #coding, #productivity, #filemanagement</t>
+          <t>#Python, #CodingTips, #DiskSpace, #Programming</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>See how to categorize your download folder using Python code. Python can sort your downloads folder by file extension safely. This script scans your directory and groups files by type. It uses pathlib to read extensions without moving anything. You can preview the structure before committing changes. This ensures no data is lost or modified accidentally. It is a safe way to plan your cleanup. Try it in a test folder first. Subscribe for practical Python tips.</t>
+          <t>Stop guessing which files take up space; let Python measure them for you. We utilize the os module to walk through your directory tree. It calculates file sizes in bytes for every item found. Then, we sort this list in descending order. The largest files appear at the very top. This helps you identify storage hogs quickly. It is a safe, read-only operation. No files are deleted or modified. Just a clean list of sizes. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,15 +722,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>See how to categorize your download folder using Python code.</t>
+          <t>Stop guessing which files take up space; let Python measure them for you.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>The Mistake</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -743,7 +743,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sort Downloads by Extension Using Python</t>
+          <t>Python: Find Large Files Fast</t>
         </is>
       </c>
       <c r="C3" t="n">

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-28T13:14:18.651119+00:00</t>
+          <t>2026-10-28T15:10:08.544625+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40693885601</t>
+          <t>40712352300</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-28T13</t>
+          <t>2026-10-28T15</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/rZl3jjL3zKk</t>
+          <t>https://youtube.com/shorts/CtA06Ebdz2A</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-28T13/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-28T15/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Python: Find Large Files Fast</t>
+          <t>Local Password Generation in Python</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stop guessing which files take up space; let Python measure them for you.</t>
+          <t>You can generate strong passwords locally using Python’s secure random module.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
@@ -578,7 +578,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Mistake</t>
+          <t>Unclassified</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Python: Find Large Files Fast</t>
+          <t>Local Password Generation in Python</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to find the largest files on your system using Python's os module. This read-only script walks through directories and sorts files by size, helping you manage disk space safely.</t>
+          <t>Learn how to generate strong, random passwords locally using Python's secrets module. This tutorial shows a simple, secure method for creating complex passwords without relying on external services.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #CodingTips, #DiskSpace, #Programming</t>
+          <t>#Python, #CyberSecurity, #Programming, #CodingTips</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Stop guessing which files take up space; let Python measure them for you. We utilize the os module to walk through your directory tree. It calculates file sizes in bytes for every item found. Then, we sort this list in descending order. The largest files appear at the very top. This helps you identify storage hogs quickly. It is a safe, read-only operation. No files are deleted or modified. Just a clean list of sizes. Subscribe for practical Python tips.</t>
+          <t>You can generate strong passwords locally using Python’s secure random module. First, import the secrets library. Define your character set including letters, digits, and symbols. Use secrets.choice to pick random characters from this set. Join them into a single string. This method runs entirely on your device, keeping your data private. It avoids external API calls and potential security risks. The output is unpredictable and robust for most applications. Always test your generated passwords in a safe environment first. This simple script demonstrates fundamental cryptographic best practices. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,15 +722,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Stop guessing which files take up space; let Python measure them for you.</t>
+          <t>You can generate strong passwords locally using Python’s secure random module.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>The Mistake</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -743,7 +743,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Python: Find Large Files Fast</t>
+          <t>Local Password Generation in Python</t>
         </is>
       </c>
       <c r="C3" t="n">

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-28T15:10:08.544625+00:00</t>
+          <t>2026-10-28T20:59:37.768709+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40712352300</t>
+          <t>40767482993</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-28T15</t>
+          <t>2026-10-28T20</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/CtA06Ebdz2A</t>
+          <t>https://youtube.com/shorts/QVE6HHRwMfs</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-28T15/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-28T20/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Local Password Generation in Python</t>
+          <t>Rename Files Safely With Python in 45 Seconds</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>You can generate strong passwords locally using Python’s secure random module.</t>
+          <t>Stop guessing file names and start renaming with Python safely.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13">
@@ -578,7 +578,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>The Mistake</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Local Password Generation in Python</t>
+          <t>Rename Files Safely With Python in 45 Seconds</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to generate strong, random passwords locally using Python's secrets module. This tutorial shows a simple, secure method for creating complex passwords without relying on external services.</t>
+          <t>Learn how to rename multiple files safely using Python's os module. This tutorial covers checking file existence and constructing new names to avoid data loss. Perfect for beginners learning file system operations.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #CyberSecurity, #Programming, #CodingTips</t>
+          <t>#Python, #CodingTips, #FileManagement, #Programming</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>You can generate strong passwords locally using Python’s secure random module. First, import the secrets library. Define your character set including letters, digits, and symbols. Use secrets.choice to pick random characters from this set. Join them into a single string. This method runs entirely on your device, keeping your data private. It avoids external API calls and potential security risks. The output is unpredictable and robust for most applications. Always test your generated passwords in a safe environment first. This simple script demonstrates fundamental cryptographic best practices. Subscribe for practical Python tips.</t>
+          <t>Stop guessing file names and start renaming with Python safely. First, import the os module to access file system tools. Use os.listdir to get a list of files in your directory. Loop through this list to process each file individually. Check if the file exists before attempting any action. Build the new name using string formatting or f-strings. Finally, use os.rename to change the name. Always verify the new name is unique. This prevents accidental overwrites of existing files. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,15 +722,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>You can generate strong passwords locally using Python’s secure random module.</t>
+          <t>Stop guessing file names and start renaming with Python safely.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>The Mistake</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -743,16 +743,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Local Password Generation in Python</t>
+          <t>Rename Files Safely With Python in 45 Seconds</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>['no-number', 'no number, date or name - the most reliable single fix']</t>
+          <t>['mobile', 'a mobile feed shows about "Rename Files Safely With Python in 45..." - check the subject survives']</t>
         </is>
       </c>
     </row>

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-28T20:59:37.768709+00:00</t>
+          <t>2026-10-28T22:56:33.982909+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40767482993</t>
+          <t>40783150813</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-28T20</t>
+          <t>2026-10-28T22</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/QVE6HHRwMfs</t>
+          <t>https://youtube.com/shorts/_oM_hlPgyx4</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-28T20/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-28T22/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rename Files Safely With Python in 45 Seconds</t>
+          <t>Python: List Folders to CSV Easily</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stop guessing file names and start renaming with Python safely.</t>
+          <t>This snippet helps you track directory names without touching your actual files.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13">
@@ -578,7 +578,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Mistake</t>
+          <t>The Impossible Claim</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rename Files Safely With Python in 45 Seconds</t>
+          <t>Python: List Folders to CSV Easily</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to rename multiple files safely using Python's os module. This tutorial covers checking file existence and constructing new names to avoid data loss. Perfect for beginners learning file system operations.</t>
+          <t>Learn how to create a simple folder inventory as a CSV file using Python. This short demonstrates how to list directories safely without modifying any existing files. Perfect for project documentation and organization.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #CodingTips, #FileManagement, #Programming</t>
+          <t>#Python, #CSV, #Productivity, #Coding</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Stop guessing file names and start renaming with Python safely. First, import the os module to access file system tools. Use os.listdir to get a list of files in your directory. Loop through this list to process each file individually. Check if the file exists before attempting any action. Build the new name using string formatting or f-strings. Finally, use os.rename to change the name. Always verify the new name is unique. This prevents accidental overwrites of existing files. Subscribe for practical Python tips.</t>
+          <t>This snippet helps you track directory names without touching your actual files. First, import the os module to access system paths. Next, iterate through the current directory using os.listdir. Check each item to ensure it is a folder, not a file. Finally, write those names to a CSV file. This creates a clean, readable inventory. It helps you track project structures easily. No complex libraries are needed here. Just standard Python tools. This method is safe and read-only. It never modifies your existing data. Perfect for quick documentation tasks. Keep your workspace organized effortlessly. Subscribe for more practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,15 +722,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Stop guessing file names and start renaming with Python safely.</t>
+          <t>This snippet helps you track directory names without touching your actual files.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>The Mistake</t>
+          <t>The Impossible Claim</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -743,7 +743,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rename Files Safely With Python in 45 Seconds</t>
+          <t>Python: List Folders to CSV Easily</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -752,7 +752,7 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>['mobile', 'a mobile feed shows about "Rename Files Safely With Python in 45..." - check the subject survives']</t>
+          <t>['no-number', 'no number, date or name - the most reliable single fix']</t>
         </is>
       </c>
     </row>

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-28T22:56:33.982909+00:00</t>
+          <t>2026-10-29T01:16:45.364942+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40783150813</t>
+          <t>40798859927</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-28T22</t>
+          <t>2026-10-29T01</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/_oM_hlPgyx4</t>
+          <t>https://youtube.com/shorts/Ys4bo3YUPM8</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-28T22/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-29T01/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Python: List Folders to CSV Easily</t>
+          <t>Export Folders to CSV in 10 Seconds</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>This snippet helps you track directory names without touching your actual files.</t>
+          <t>Stop manually typing folder names; let Python create a clean CSV list for you.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
@@ -578,7 +578,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Impossible Claim</t>
+          <t>The Mistake</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Python: List Folders to CSV Easily</t>
+          <t>Export Folders to CSV in 10 Seconds</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to create a simple folder inventory as a CSV file using Python. This short demonstrates how to list directories safely without modifying any existing files. Perfect for project documentation and organization.</t>
+          <t>Learn how to create a simple folder inventory as a CSV file using Python. This safe technique lists directory names without modifying existing files.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #CSV, #Productivity, #Coding</t>
+          <t>#Python, #CSV, #FileManagement, #CodingTips</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>This snippet helps you track directory names without touching your actual files. First, import the os module to access system paths. Next, iterate through the current directory using os.listdir. Check each item to ensure it is a folder, not a file. Finally, write those names to a CSV file. This creates a clean, readable inventory. It helps you track project structures easily. No complex libraries are needed here. Just standard Python tools. This method is safe and read-only. It never modifies your existing data. Perfect for quick documentation tasks. Keep your workspace organized effortlessly. Subscribe for more practical Python tips.</t>
+          <t>Stop manually typing folder names; let Python create a clean CSV list for you. Import the os and csv modules to handle file operations. Create a list to store each subdirectory name found. Loop through the directory contents using os.listdir. Check if each item is a directory with os.path.isdir. Write the names to a new CSV file using csv.writer. This creates a clean, readable inventory without touching original data. It is perfect for organizing large projects. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,15 +722,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>This snippet helps you track directory names without touching your actual files.</t>
+          <t>Stop manually typing folder names; let Python create a clean CSV list for you.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>The Impossible Claim</t>
+          <t>The Mistake</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -743,18 +743,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Python: List Folders to CSV Easily</t>
+          <t>Export Folders to CSV in 10 Seconds</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>['no-number', 'no number, date or name - the most reliable single fix']</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-29T01:16:45.364942+00:00</t>
+          <t>2026-10-29T03:04:30.098469+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40798859927</t>
+          <t>40809496465</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-29T01</t>
+          <t>2026-10-29T02</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/Ys4bo3YUPM8</t>
+          <t>https://youtube.com/shorts/cWVKuRW2xDs</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-29T01/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-29T02/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Export Folders to CSV in 10 Seconds</t>
+          <t>Python: Compare Two Text Files Fast</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stop manually typing folder names; let Python create a clean CSV list for you.</t>
+          <t>Stop manually checking differences between two text files.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Export Folders to CSV in 10 Seconds</t>
+          <t>Python: Compare Two Text Files Fast</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to create a simple folder inventory as a CSV file using Python. This safe technique lists directory names without modifying existing files.</t>
+          <t>Learn how to compare two text files using Python's difflib module. This tutorial shows a safe, read-only method to identify differences without altering original data. Perfect for developers needing to verify file consistency.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #CSV, #FileManagement, #CodingTips</t>
+          <t>#Python, #Coding, #DataAnalysis, #ProgrammingTips</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Stop manually typing folder names; let Python create a clean CSV list for you. Import the os and csv modules to handle file operations. Create a list to store each subdirectory name found. Loop through the directory contents using os.listdir. Check if each item is a directory with os.path.isdir. Write the names to a new CSV file using csv.writer. This creates a clean, readable inventory without touching original data. It is perfect for organizing large projects. Subscribe for practical Python tips.</t>
+          <t>Stop manually checking differences between two text files. Python makes comparing file contents quick and accurate. We will use the difflib module to find exact differences. First, read both files into memory as strings. Next, generate a unified diff object. Finally, print the changes clearly. This method highlights additions and deletions precisely. It is perfect for verifying data integrity. You avoid manual errors and save significant time. The code is simple and safe. It only reads files, never modifies them. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,11 +722,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Stop manually typing folder names; let Python create a clean CSV list for you.</t>
+          <t>Stop manually checking differences between two text files.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -743,14 +743,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Export Folders to CSV in 10 Seconds</t>
+          <t>Python: Compare Two Text Files Fast</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>['no-number', 'no number, date or name - the most reliable single fix']</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-29T03:04:30.098469+00:00</t>
+          <t>2026-10-29T05:04:14.016185+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40809496465</t>
+          <t>40820690947</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-29T02</t>
+          <t>2026-10-29T04</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/cWVKuRW2xDs</t>
+          <t>https://youtube.com/shorts/BstJ0Tarb7E</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-29T02/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-29T04/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Python: Compare Two Text Files Fast</t>
+          <t>Show First 5 Rows of a CSV</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stop manually checking differences between two text files.</t>
+          <t>Quickly inspect your CSV file using this simple Python code.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
@@ -578,7 +578,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Mistake</t>
+          <t>Unclassified</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Python: Compare Two Text Files Fast</t>
+          <t>Show First 5 Rows of a CSV</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to compare two text files using Python's difflib module. This tutorial shows a safe, read-only method to identify differences without altering original data. Perfect for developers needing to verify file consistency.</t>
+          <t>Learn how to efficiently preview the first five rows of a CSV file using Python and pandas. This method helps you inspect data structure without loading the entire dataset.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #Coding, #DataAnalysis, #ProgrammingTips</t>
+          <t>#Python, #Pandas, #DataScience, #CodingTips</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Stop manually checking differences between two text files. Python makes comparing file contents quick and accurate. We will use the difflib module to find exact differences. First, read both files into memory as strings. Next, generate a unified diff object. Finally, print the changes clearly. This method highlights additions and deletions precisely. It is perfect for verifying data integrity. You avoid manual errors and save significant time. The code is simple and safe. It only reads files, never modifies them. Subscribe for practical Python tips.</t>
+          <t>Quickly inspect your CSV file using this simple Python code. Instead of loading massive datasets, use pandas to preview your data. Import pandas and read the file using the read_csv function. Specify the head method with five as the argument. This displays exactly the top five rows. It is efficient and safe for quick inspection. You can verify column names and data types immediately. This technique saves memory and time. Use it before processing large files. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,15 +722,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Stop manually checking differences between two text files.</t>
+          <t>Quickly inspect your CSV file using this simple Python code.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>The Mistake</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -743,18 +743,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Python: Compare Two Text Files Fast</t>
+          <t>Show First 5 Rows of a CSV</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>['no-number', 'no number, date or name - the most reliable single fix']</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-29T05:04:14.016185+00:00</t>
+          <t>2026-10-29T09:09:18.464198+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40820690947</t>
+          <t>40846679895</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-29T04</t>
+          <t>2026-10-29T09</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/BstJ0Tarb7E</t>
+          <t>https://youtube.com/shorts/Esw5e9O2AM0</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-29T04/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-29T09/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Show First 5 Rows of a CSV</t>
+          <t>Move Files by Extension Safely in Python</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Quickly inspect your CSV file using this simple Python code.</t>
+          <t>You can sort your downloads folder by file extension using this simple Python script.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13">
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Show First 5 Rows of a CSV</t>
+          <t>Move Files by Extension Safely in Python</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to efficiently preview the first five rows of a CSV file using Python and pandas. This method helps you inspect data structure without loading the entire dataset.</t>
+          <t>Learn how to safely organize your downloads folder by file extension using Python. This short demonstrates a preview-first approach to moving files into categorized subdirectories without altering original data.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #Pandas, #DataScience, #CodingTips</t>
+          <t>#PythonTips, #FileManagement, #Automation, #CodingShorts</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Quickly inspect your CSV file using this simple Python code. Instead of loading massive datasets, use pandas to preview your data. Import pandas and read the file using the read_csv function. Specify the head method with five as the argument. This displays exactly the top five rows. It is efficient and safe for quick inspection. You can verify column names and data types immediately. This technique saves memory and time. Use it before processing large files. Subscribe for practical Python tips.</t>
+          <t>You can sort your downloads folder by file extension using this simple Python script. First, list files in your downloads folder. Check each file's extension. Then, create target folders for each type. Use preview mode to verify paths before moving. This ensures no data is lost or modified unexpectedly. The script handles common formats like images and documents. It keeps your workspace clean and structured. You can customize the logic for specific needs. Always test with a small batch first. This method saves time and reduces clutter. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,11 +722,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Quickly inspect your CSV file using this simple Python code.</t>
+          <t>You can sort your downloads folder by file extension using this simple Python script.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -743,14 +743,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Show First 5 Rows of a CSV</t>
+          <t>Move Files by Extension Safely in Python</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>['no-number', 'no number, date or name - the most reliable single fix']</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-29T09:09:18.464198+00:00</t>
+          <t>2026-10-29T11:03:31.291875+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40846679895</t>
+          <t>40861718613</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-29T09</t>
+          <t>2026-10-29T10</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/Esw5e9O2AM0</t>
+          <t>https://youtube.com/shorts/6MMXUuESeLM</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-29T09/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-29T10/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Move Files by Extension Safely in Python</t>
+          <t>Safe Python File Renaming</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>You can sort your downloads folder by file extension using this simple Python script.</t>
+          <t>Renaming many files can corrupt data if you do it wrong.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Move Files by Extension Safely in Python</t>
+          <t>Safe Python File Renaming</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to safely organize your downloads folder by file extension using Python. This short demonstrates a preview-first approach to moving files into categorized subdirectories without altering original data.</t>
+          <t>Learn how to safely rename multiple files using Python's os.rename. Discover how to prevent data loss by checking for existing targets and handling exceptions. This tutorial covers safe batch renaming techniques without modifying user data.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#PythonTips, #FileManagement, #Automation, #CodingShorts</t>
+          <t>#Python, #Coding, #FileManagement, #Programming</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>You can sort your downloads folder by file extension using this simple Python script. First, list files in your downloads folder. Check each file's extension. Then, create target folders for each type. Use preview mode to verify paths before moving. This ensures no data is lost or modified unexpectedly. The script handles common formats like images and documents. It keeps your workspace clean and structured. You can customize the logic for specific needs. Always test with a small batch first. This method saves time and reduces clutter. Subscribe for practical Python tips.</t>
+          <t>Renaming many files can corrupt data if you do it wrong. Python’s os.rename is powerful but requires careful handling. Avoid data loss when batch renaming files in Python scripts. Learn the safe way to rename multiple files using Python. Here is how to rename files safely without losing data. Always check if the target file already exists before renaming. Use a try-except block to catch potential collisions. This prevents accidental overwriting of existing files. Keep your original filenames intact during testing. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,11 +722,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>You can sort your downloads folder by file extension using this simple Python script.</t>
+          <t>Renaming many files can corrupt data if you do it wrong.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Move Files by Extension Safely in Python</t>
+          <t>Safe Python File Renaming</t>
         </is>
       </c>
       <c r="C3" t="n">

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-29T11:03:31.291875+00:00</t>
+          <t>2026-10-29T15:12:30.691414+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40861718613</t>
+          <t>40898331366</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-29T10</t>
+          <t>2026-10-29T15</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/6MMXUuESeLM</t>
+          <t>https://youtube.com/shorts/D--f8eYjUrU</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-29T10/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-29T15/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Safe Python File Renaming</t>
+          <t>Python: Count File Types in Any Folder</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Renaming many files can corrupt data if you do it wrong.</t>
+          <t>This Python snippet counts file types in your folder.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13">
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Safe Python File Renaming</t>
+          <t>Python: Count File Types in Any Folder</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to safely rename multiple files using Python's os.rename. Discover how to prevent data loss by checking for existing targets and handling exceptions. This tutorial covers safe batch renaming techniques without modifying user data.</t>
+          <t>Learn how to count file types in a folder using Python. This tutorial demonstrates a safe, read-only script using os.walk and a dictionary to tally file extensions. Perfect for organizing or analyzing large datasets.</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Renaming many files can corrupt data if you do it wrong. Python’s os.rename is powerful but requires careful handling. Avoid data loss when batch renaming files in Python scripts. Learn the safe way to rename multiple files using Python. Here is how to rename files safely without losing data. Always check if the target file already exists before renaming. Use a try-except block to catch potential collisions. This prevents accidental overwriting of existing files. Keep your original filenames intact during testing. Subscribe for practical Python tips.</t>
+          <t>This Python snippet counts file types in your folder. Use Python to count file types in any folder quickly. First, import the os module to access directory operations. Next, iterate through the folder using os.walk. Extract the file extension from each filename. Finally, update a dictionary to tally each type. This method is safe and read-only. It helps you analyze large directories efficiently without modifying files. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,11 +722,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Renaming many files can corrupt data if you do it wrong.</t>
+          <t>This Python snippet counts file types in your folder.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Safe Python File Renaming</t>
+          <t>Python: Count File Types in Any Folder</t>
         </is>
       </c>
       <c r="C3" t="n">

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-29T15:12:30.691414+00:00</t>
+          <t>2026-10-29T17:10:06.821514+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40898331366</t>
+          <t>40917799164</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-29T15</t>
+          <t>2026-10-29T17</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/D--f8eYjUrU</t>
+          <t>https://youtube.com/shorts/-0k7ph4YgrA</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-29T15/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-29T17/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Python: Count File Types in Any Folder</t>
+          <t>Find Disk Hoggers with Python in 30 Seconds</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>This Python snippet counts file types in your folder.</t>
+          <t>Stop guessing which files eat your storage; Python can scan them instantly.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>37</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13">
@@ -578,7 +578,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>The Mistake</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Python: Count File Types in Any Folder</t>
+          <t>Find Disk Hoggers with Python in 30 Seconds</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to count file types in a folder using Python. This tutorial demonstrates a safe, read-only script using os.walk and a dictionary to tally file extensions. Perfect for organizing or analyzing large datasets.</t>
+          <t>Learn how to identify files consuming the most disk space using Python's os module. This safe, read-only script sorts files by size to help you manage storage efficiently.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #Coding, #FileManagement, #Programming</t>
+          <t>#Python, #CodingTips, #DiskManagement, #Scripting</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>This Python snippet counts file types in your folder. Use Python to count file types in any folder quickly. First, import the os module to access directory operations. Next, iterate through the folder using os.walk. Extract the file extension from each filename. Finally, update a dictionary to tally each type. This method is safe and read-only. It helps you analyze large directories efficiently without modifying files. Subscribe for practical Python tips.</t>
+          <t>Stop guessing which files eat your storage; Python can scan them instantly. We will use the os module to walk through a directory tree. This code collects file paths and sizes without touching the actual data. It sorts them so the largest items appear first. This helps you identify heavy files quickly. It is safe because it only reads metadata. You can adapt the path to check specific folders easily. No deletion happens, so your data remains untouched. This simple logic is perfect for quick system audits. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,15 +722,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>This Python snippet counts file types in your folder.</t>
+          <t>Stop guessing which files eat your storage; Python can scan them instantly.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>The Mistake</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -743,16 +743,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Python: Count File Types in Any Folder</t>
+          <t>Find Disk Hoggers with Python in 30 Seconds</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>['no-number', 'no number, date or name - the most reliable single fix']</t>
+          <t>['mobile', 'a mobile feed shows about "Find Disk Hoggers with Python in 30..." - check the subject survives']</t>
         </is>
       </c>
     </row>

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-29T17:10:06.821514+00:00</t>
+          <t>2026-10-29T19:08:30.537044+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40917799164</t>
+          <t>40936719325</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-29T17</t>
+          <t>2026-10-29T19</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/-0k7ph4YgrA</t>
+          <t>https://youtube.com/shorts/0k0JMctd9Gs</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-29T17/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-29T19/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Find Disk Hoggers with Python in 30 Seconds</t>
+          <t>Diff Text Files Using Python's difflib</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stop guessing which files eat your storage; Python can scan them instantly.</t>
+          <t>Here is how to safely diff files in Python.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>53</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
@@ -578,7 +578,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Mistake</t>
+          <t>Unclassified</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Find Disk Hoggers with Python in 30 Seconds</t>
+          <t>Diff Text Files Using Python's difflib</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to identify files consuming the most disk space using Python's os module. This safe, read-only script sorts files by size to help you manage storage efficiently.</t>
+          <t>Learn how to compare two text files using Python's difflib module. This tutorial demonstrates a safe, read-only method to identify differences without modifying original data. Ideal for developers needing efficient file comparison scripts.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #CodingTips, #DiskManagement, #Scripting</t>
+          <t>#Python, #Coding, #Difflib, #ProgrammingTips</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Stop guessing which files eat your storage; Python can scan them instantly. We will use the os module to walk through a directory tree. This code collects file paths and sizes without touching the actual data. It sorts them so the largest items appear first. This helps you identify heavy files quickly. It is safe because it only reads metadata. You can adapt the path to check specific folders easily. No deletion happens, so your data remains untouched. This simple logic is perfect for quick system audits. Subscribe for practical Python tips.</t>
+          <t>Here is how to safely diff files in Python. Instead of manual checking, use the built-in difflib module. It provides robust tools for analyzing differences. Read both files into memory first. Then pass the text lines to SequenceMatcher. This object calculates similarity ratios. You can also generate unified diffs directly. This helps identify exact changes. It is perfect for version control tasks. The code is concise and readable. No external libraries are required. It runs efficiently on large files. This approach prevents data loss. It keeps your original files intact. Use this technique for reliable comparisons. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,15 +722,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Stop guessing which files eat your storage; Python can scan them instantly.</t>
+          <t>Here is how to safely diff files in Python.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>The Mistake</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -743,16 +743,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Find Disk Hoggers with Python in 30 Seconds</t>
+          <t>Diff Text Files Using Python's difflib</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>['mobile', 'a mobile feed shows about "Find Disk Hoggers with Python in 30..." - check the subject survives']</t>
+          <t>['no-number', 'no number, date or name - the most reliable single fix']</t>
         </is>
       </c>
     </row>

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-29T19:08:30.537044+00:00</t>
+          <t>2026-10-29T21:01:33.483353+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40936719325</t>
+          <t>40953383213</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-29T19</t>
+          <t>2026-10-29T20</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/0k0JMctd9Gs</t>
+          <t>https://youtube.com/shorts/1oTMtNLrGwc</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-29T19/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-29T20/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Diff Text Files Using Python's difflib</t>
+          <t>Python Folder Inventory CSV Guide</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Here is how to safely diff files in Python.</t>
+          <t>Learn how to list your directory structure into a clean CSV file safely.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13">
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Diff Text Files Using Python's difflib</t>
+          <t>Python Folder Inventory CSV Guide</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to compare two text files using Python's difflib module. This tutorial demonstrates a safe, read-only method to identify differences without modifying original data. Ideal for developers needing efficient file comparison scripts.</t>
+          <t>Learn how to create a simple folder inventory as a CSV file using Python. This tutorial shows a safe, read-only approach to listing files and their sizes.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #Coding, #Difflib, #ProgrammingTips</t>
+          <t>#Python, #Coding, #FileManagement, #CSV</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Here is how to safely diff files in Python. Instead of manual checking, use the built-in difflib module. It provides robust tools for analyzing differences. Read both files into memory first. Then pass the text lines to SequenceMatcher. This object calculates similarity ratios. You can also generate unified diffs directly. This helps identify exact changes. It is perfect for version control tasks. The code is concise and readable. No external libraries are required. It runs efficiently on large files. This approach prevents data loss. It keeps your original files intact. Use this technique for reliable comparisons. Subscribe for practical Python tips.</t>
+          <t>Learn how to list your directory structure into a clean CSV file safely. This script lists files in the current directory, capturing names and sizes. It writes the data to a new CSV file called inventory.csv. The code uses the os module to read directory entries safely. It never deletes or modifies your original files, ensuring your data remains untouched. This method is perfect for quick backups or auditing. You can easily extend this to subdirectories later. Watch how simple it is to organize your digital workspace. Subscribe for more practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,11 +722,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Here is how to safely diff files in Python.</t>
+          <t>Learn how to list your directory structure into a clean CSV file safely.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -743,11 +743,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Diff Text Files Using Python's difflib</t>
+          <t>Python Folder Inventory CSV Guide</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-29T21:01:33.483353+00:00</t>
+          <t>2026-10-29T22:56:47.775590+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40953383213</t>
+          <t>40969186209</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-29T20</t>
+          <t>2026-10-29T22</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/1oTMtNLrGwc</t>
+          <t>https://youtube.com/shorts/ygLwiRsvWFg</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-29T20/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-29T22/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Python Folder Inventory CSV Guide</t>
+          <t>Diff Two Files with Python difflib</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Learn how to list your directory structure into a clean CSV file safely.</t>
+          <t>You can spot differences between two files using difflib.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Python Folder Inventory CSV Guide</t>
+          <t>Diff Two Files with Python difflib</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to create a simple folder inventory as a CSV file using Python. This tutorial shows a safe, read-only approach to listing files and their sizes.</t>
+          <t>Learn how to compare two text files using Python's difflib module. This read-only technique helps you identify differences without altering your data. Perfect for debugging or version control checks.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #Coding, #FileManagement, #CSV</t>
+          <t>#Python, #Coding, #Difflib, #ProgrammingTips</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Learn how to list your directory structure into a clean CSV file safely. This script lists files in the current directory, capturing names and sizes. It writes the data to a new CSV file called inventory.csv. The code uses the os module to read directory entries safely. It never deletes or modifies your original files, ensuring your data remains untouched. This method is perfect for quick backups or auditing. You can easily extend this to subdirectories later. Watch how simple it is to organize your digital workspace. Subscribe for more practical Python tips.</t>
+          <t>You can spot differences between two files using difflib. Open both files and read their lines into lists. Import difflib and run SequenceMatcher. It calculates the ratio of similarity. Iterate through opcodes to find replaced or inserted lines. Print those specific changes to your console. This method is safe and read-only. You never modify the original data. It works for any text format. Learn this practical trick today. Subscribe for more practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,11 +722,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Learn how to list your directory structure into a clean CSV file safely.</t>
+          <t>You can spot differences between two files using difflib.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -743,11 +743,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Python Folder Inventory CSV Guide</t>
+          <t>Diff Two Files with Python difflib</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-29T22:56:47.775590+00:00</t>
+          <t>2026-10-30T01:20:36.834445+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40969186209</t>
+          <t>40984671755</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-29T22</t>
+          <t>2026-10-30T01</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/ygLwiRsvWFg</t>
+          <t>https://youtube.com/shorts/iLDVoY_aKNg</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-29T22/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-30T01/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Diff Two Files with Python difflib</t>
+          <t>Python: List Folder Files to CSV</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>You can spot differences between two files using difflib.</t>
+          <t>Here is how to export your folder structure to a spreadsheet.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13">
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Diff Two Files with Python difflib</t>
+          <t>Python: List Folder Files to CSV</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to compare two text files using Python's difflib module. This read-only technique helps you identify differences without altering your data. Perfect for debugging or version control checks.</t>
+          <t>Learn how to create a simple folder inventory as a CSV file using Python. This safe script lists all files and directories without modifying your data. Perfect for backups, audits, and organization. #Python #Automation #CSV #Coding</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #Coding, #Difflib, #ProgrammingTips</t>
+          <t>#Python, #Automation, #CSV, #Coding</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>You can spot differences between two files using difflib. Open both files and read their lines into lists. Import difflib and run SequenceMatcher. It calculates the ratio of similarity. Iterate through opcodes to find replaced or inserted lines. Print those specific changes to your console. This method is safe and read-only. You never modify the original data. It works for any text format. Learn this practical trick today. Subscribe for more practical Python tips.</t>
+          <t>Here is how to export your folder structure to a spreadsheet. Python solves this instantly. Use the os module to walk through directories. Capture filenames and paths. Write them directly to a CSV file. This creates a perfect inventory. No manual copying required. The code is short and safe. It only reads data. It never modifies your files. You get a clean list. Great for backups or audits. It works on any operating system. The output is easy to read. You can open it in Excel. This saves you significant time. It is a fundamental automation task. Learn this simple script today. It handles nested folders too. The process is completely safe. No permissions needed for reading. Just run the script. Check your output folder. The CSV will be ready.</t>
         </is>
       </c>
     </row>
@@ -722,11 +722,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>You can spot differences between two files using difflib.</t>
+          <t>Here is how to export your folder structure to a spreadsheet.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -743,11 +743,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Diff Two Files with Python difflib</t>
+          <t>Python: List Folder Files to CSV</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-30T01:20:36.834445+00:00</t>
+          <t>2026-10-30T03:04:13.255305+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40984671755</t>
+          <t>40994805577</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-30T01</t>
+          <t>2026-10-30T03</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/iLDVoY_aKNg</t>
+          <t>https://youtube.com/shorts/Wv48h-bQY7Q</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-30T01/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-30T03/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Python: List Folder Files to CSV</t>
+          <t>Python: Sort Downloads by Extension</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Here is how to export your folder structure to a spreadsheet.</t>
+          <t>You can preview how to sort downloads by file extension safely.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Python: List Folder Files to CSV</t>
+          <t>Python: Sort Downloads by Extension</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to create a simple folder inventory as a CSV file using Python. This safe script lists all files and directories without modifying your data. Perfect for backups, audits, and organization. #Python #Automation #CSV #Coding</t>
+          <t>Learn how to preview organizing your downloads folder by file extension using Python. This safe technique groups files by their suffix without moving or modifying them, preventing accidental data loss. Perfect for learning file handling and directory operations.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #Automation, #CSV, #Coding</t>
+          <t>#python, #coding, #filemanagement, #productivity</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Here is how to export your folder structure to a spreadsheet. Python solves this instantly. Use the os module to walk through directories. Capture filenames and paths. Write them directly to a CSV file. This creates a perfect inventory. No manual copying required. The code is short and safe. It only reads data. It never modifies your files. You get a clean list. Great for backups or audits. It works on any operating system. The output is easy to read. You can open it in Excel. This saves you significant time. It is a fundamental automation task. Learn this simple script today. It handles nested folders too. The process is completely safe. No permissions needed for reading. Just run the script. Check your output folder. The CSV will be ready.</t>
+          <t>You can preview how to sort downloads by file extension safely. This Python script reads a directory and groups files by their suffix. It creates a dictionary where keys are extensions and values are file lists. Crucially, it only prints the structure; it never moves or modifies anything. You verify the logic before executing any actual file operations. This approach prevents accidental data loss during cleanup. It provides a clear visual map of your download folder. Check the code below to see how it works. Subscribe for practical Python tips that keep your files safe and organized efficiently every single day.</t>
         </is>
       </c>
     </row>
@@ -722,11 +722,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Here is how to export your folder structure to a spreadsheet.</t>
+          <t>You can preview how to sort downloads by file extension safely.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -743,11 +743,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Python: List Folder Files to CSV</t>
+          <t>Python: Sort Downloads by Extension</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-30T03:04:13.255305+00:00</t>
+          <t>2026-10-30T05:03:56.466916+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40994805577</t>
+          <t>41005840740</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-30T03</t>
+          <t>2026-10-30T04</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/Wv48h-bQY7Q</t>
+          <t>https://youtube.com/shorts/nKRrhLELl8M</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-30T03/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-30T04/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Python: Sort Downloads by Extension</t>
+          <t>Find Empty Folders Safely in Python</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>You can preview how to sort downloads by file extension safely.</t>
+          <t>Discover empty folders on your system without touching them using Python.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
@@ -578,7 +578,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>The Impossible Claim</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Python: Sort Downloads by Extension</t>
+          <t>Find Empty Folders Safely in Python</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to preview organizing your downloads folder by file extension using Python. This safe technique groups files by their suffix without moving or modifying them, preventing accidental data loss. Perfect for learning file handling and directory operations.</t>
+          <t>Learn a safe Python technique to identify empty folders without modifying or deleting any files. This tutorial uses os.walk to traverse directories and check for emptiness. Perfect for cleaning up project structures safely.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#python, #coding, #filemanagement, #productivity</t>
+          <t>#Python, #CodingTips, #FileManagement, #LearnPython</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>You can preview how to sort downloads by file extension safely. This Python script reads a directory and groups files by their suffix. It creates a dictionary where keys are extensions and values are file lists. Crucially, it only prints the structure; it never moves or modifies anything. You verify the logic before executing any actual file operations. This approach prevents accidental data loss during cleanup. It provides a clear visual map of your download folder. Check the code below to see how it works. Subscribe for practical Python tips that keep your files safe and organized efficiently every single day.</t>
+          <t>Discover empty folders on your system without touching them using Python. First, import the os module to access directory functions. Create a recursive walker to traverse your file tree. Check if the current folder contains no files or subdirectories. Print the path if it is completely empty. This method only reads data, ensuring no changes occur. It helps you organize storage effectively. Always verify paths before any manual action. Subscribe for more practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,15 +722,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>You can preview how to sort downloads by file extension safely.</t>
+          <t>Discover empty folders on your system without touching them using Python.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>The Impossible Claim</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -743,7 +743,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Python: Sort Downloads by Extension</t>
+          <t>Find Empty Folders Safely in Python</t>
         </is>
       </c>
       <c r="C3" t="n">

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-30T05:03:56.466916+00:00</t>
+          <t>2026-10-30T07:15:30.229177+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>41005840740</t>
+          <t>41018606229</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-30T04</t>
+          <t>2026-10-30T07</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/nKRrhLELl8M</t>
+          <t>https://youtube.com/shorts/KF3xpmO-mmE</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-30T04/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-30T07/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Find Empty Folders Safely in Python</t>
+          <t>Count File Types in Python in 30 Seconds</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Discover empty folders on your system without touching them using Python.</t>
+          <t>You can count every file type in a folder using just a simple Python dictionary.</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Impossible Claim</t>
+          <t>Unclassified</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Find Empty Folders Safely in Python</t>
+          <t>Count File Types in Python in 30 Seconds</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn a safe Python technique to identify empty folders without modifying or deleting any files. This tutorial uses os.walk to traverse directories and check for emptiness. Perfect for cleaning up project structures safely.</t>
+          <t>Learn how to count file types in a folder using Python. This short tutorial shows you how to use os.listdir and dictionaries to tally file extensions efficiently. Perfect for beginners looking to automate file management tasks.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #CodingTips, #FileManagement, #LearnPython</t>
+          <t>#Python, #Programming, #CodingTips, #FileManagement</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Discover empty folders on your system without touching them using Python. First, import the os module to access directory functions. Create a recursive walker to traverse your file tree. Check if the current folder contains no files or subdirectories. Print the path if it is completely empty. This method only reads data, ensuring no changes occur. It helps you organize storage effectively. Always verify paths before any manual action. Subscribe for more practical Python tips.</t>
+          <t>You can count every file type in a folder using just a simple Python dictionary. First, import the os module to access the file system. Next, use os.listdir to get all items in the current directory. Then, extract the file extension from each name using split. Finally, increment the count for each unique extension in your dictionary. This approach is efficient and easy to understand. You can easily modify the path variable to target any specific folder on your system. It is a great way to audit your project files quickly. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Discover empty folders on your system without touching them using Python.</t>
+          <t>You can count every file type in a folder using just a simple Python dictionary.</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -730,7 +730,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>The Impossible Claim</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -743,18 +743,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Find Empty Folders Safely in Python</t>
+          <t>Count File Types in Python in 30 Seconds</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>['no-number', 'no number, date or name - the most reliable single fix']</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-30T07:15:30.229177+00:00</t>
+          <t>2026-10-30T09:08:26.914976+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>41018606229</t>
+          <t>41030639254</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-30T07</t>
+          <t>2026-10-30T09</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/KF3xpmO-mmE</t>
+          <t>https://youtube.com/shorts/U3FdorfIbQk</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-30T07/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-30T09/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Count File Types in Python in 30 Seconds</t>
+          <t>Preview File Sorting in Python</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>You can count every file type in a folder using just a simple Python dictionary.</t>
+          <t>See exactly how your downloads organize by type before executing changes.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13">
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Count File Types in Python in 30 Seconds</t>
+          <t>Preview File Sorting in Python</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to count file types in a folder using Python. This short tutorial shows you how to use os.listdir and dictionaries to tally file extensions efficiently. Perfect for beginners looking to automate file management tasks.</t>
+          <t>Learn how to safely preview file organization by extension using Python. This script lists files without modifying them, ensuring you verify the structure before making changes.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #Programming, #CodingTips, #FileManagement</t>
+          <t>#Python, #Productivity, #CodingTips, #FileManagement</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>You can count every file type in a folder using just a simple Python dictionary. First, import the os module to access the file system. Next, use os.listdir to get all items in the current directory. Then, extract the file extension from each name using split. Finally, increment the count for each unique extension in your dictionary. This approach is efficient and easy to understand. You can easily modify the path variable to target any specific folder on your system. It is a great way to audit your project files quickly. Subscribe for practical Python tips.</t>
+          <t>See exactly how your downloads organize by type before executing changes. Python lets you list file extensions without touching your actual files. We use os.listdir to read the current directory safely. Then we extract extensions using os.path.splitext. This groups files by type for review. No files are moved or deleted during this preview. It ensures accuracy before any real organization happens. Check your list carefully first. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,11 +722,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>You can count every file type in a folder using just a simple Python dictionary.</t>
+          <t>See exactly how your downloads organize by type before executing changes.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -743,14 +743,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Count File Types in Python in 30 Seconds</t>
+          <t>Preview File Sorting in Python</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>['no-number', 'no number, date or name - the most reliable single fix']</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-30T09:08:26.914976+00:00</t>
+          <t>2026-10-30T11:02:12.929105+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>41030639254</t>
+          <t>41044433667</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-30T09</t>
+          <t>2026-10-30T10</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/U3FdorfIbQk</t>
+          <t>https://youtube.com/shorts/l0wmLqfFRjc</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-30T09/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-30T10/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Preview File Sorting in Python</t>
+          <t>Diff Two Text Files in Python</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>See exactly how your downloads organize by type before executing changes.</t>
+          <t>You can find differences between two text files in Python without installing extra packages.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
@@ -578,7 +578,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>The Impossible Claim</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Preview File Sorting in Python</t>
+          <t>Diff Two Text Files in Python</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to safely preview file organization by extension using Python. This script lists files without modifying them, ensuring you verify the structure before making changes.</t>
+          <t>Learn how to compare two text files using Python's built-in difflib module. This safe method highlights differences without modifying original files. Perfect for developers and data analysts.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #Productivity, #CodingTips, #FileManagement</t>
+          <t>#Python, #Coding, #Programming, #Difflib</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>See exactly how your downloads organize by type before executing changes. Python lets you list file extensions without touching your actual files. We use os.listdir to read the current directory safely. Then we extract extensions using os.path.splitext. This groups files by type for review. No files are moved or deleted during this preview. It ensures accuracy before any real organization happens. Check your list carefully first. Subscribe for practical Python tips.</t>
+          <t>You can find differences between two text files in Python without installing extra packages. The difflib module includes a unified_diff function that compares file lines. First, read both files into memory using the standard open function. Then, pass the line lists to unified_diff. Finally, iterate through the results to print only the changed lines. This method is safe because it never modifies your original data. It works on any text format and runs quickly. By using built-in tools, you avoid complex dependencies. This approach is reliable for checking version changes or validating data. It helps you verify accuracy without manual effort. The code is simple and easy to adapt for your projects. You can extend it to highlight specific patterns. This technique saves time during debugging. It ensures your text.</t>
         </is>
       </c>
     </row>
@@ -722,15 +722,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>See exactly how your downloads organize by type before executing changes.</t>
+          <t>You can find differences between two text files in Python without installing extra packages.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>The Impossible Claim</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -743,7 +743,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Preview File Sorting in Python</t>
+          <t>Diff Two Text Files in Python</t>
         </is>
       </c>
       <c r="C3" t="n">

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-30T11:02:12.929105+00:00</t>
+          <t>2026-10-30T13:14:17.056418+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>41044433667</t>
+          <t>41060832962</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-30T10</t>
+          <t>2026-10-30T13</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/l0wmLqfFRjc</t>
+          <t>https://youtube.com/shorts/VQhsZ03Q9So</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-30T10/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-30T13/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Diff Two Text Files in Python</t>
+          <t>Python: Find Largest Files Safely</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>You can find differences between two text files in Python without installing extra packages.</t>
+          <t>You can list the largest files in any directory using simple Python standard libraries.</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Impossible Claim</t>
+          <t>Unclassified</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Diff Two Text Files in Python</t>
+          <t>Python: Find Largest Files Safely</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to compare two text files using Python's built-in difflib module. This safe method highlights differences without modifying original files. Perfect for developers and data analysts.</t>
+          <t>Learn how to find the largest files in a directory using Python's os module. This safe technique helps you audit disk space without modifying any data. Perfect for developers and data scientists.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #Coding, #Programming, #Difflib</t>
+          <t>#python, #programming, #diskusage, #codingtips</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>You can find differences between two text files in Python without installing extra packages. The difflib module includes a unified_diff function that compares file lines. First, read both files into memory using the standard open function. Then, pass the line lists to unified_diff. Finally, iterate through the results to print only the changed lines. This method is safe because it never modifies your original data. It works on any text format and runs quickly. By using built-in tools, you avoid complex dependencies. This approach is reliable for checking version changes or validating data. It helps you verify accuracy without manual effort. The code is simple and easy to adapt for your projects. You can extend it to highlight specific patterns. This technique saves time during debugging. It ensures your text.</t>
+          <t>You can list the largest files in any directory using simple Python standard libraries. First, use os.walk to traverse the folder structure recursively. Then, calculate each file size using os.path.getsize. Store these values in a dictionary for easy sorting. Finally, sort the dictionary by size in descending order. This identifies the largest files without touching them. It is a safe way to audit disk usage. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>You can find differences between two text files in Python without installing extra packages.</t>
+          <t>You can list the largest files in any directory using simple Python standard libraries.</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -730,7 +730,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>The Impossible Claim</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -743,7 +743,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Diff Two Text Files in Python</t>
+          <t>Python: Find Largest Files Safely</t>
         </is>
       </c>
       <c r="C3" t="n">

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-30T13:14:17.056418+00:00</t>
+          <t>2026-10-30T15:10:30.068107+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>41060832962</t>
+          <t>41077536495</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-30T13</t>
+          <t>2026-10-30T15</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/VQhsZ03Q9So</t>
+          <t>https://youtube.com/shorts/K5z__HAPHZk</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-30T13/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-30T15/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Python: Find Largest Files Safely</t>
+          <t>Python: List Empty Folders Safely</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>You can list the largest files in any directory using simple Python standard libraries.</t>
+          <t>You can scan directories for empty folders using pure Python.</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Python: Find Largest Files Safely</t>
+          <t>Python: List Empty Folders Safely</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to find the largest files in a directory using Python's os module. This safe technique helps you audit disk space without modifying any data. Perfect for developers and data scientists.</t>
+          <t>Learn how to use Python's os.walk module to identify empty folders. This read-only technique ensures your data remains untouched while helping you organize your file system. Perfect for system maintenance and cleanup planning.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#python, #programming, #diskusage, #codingtips</t>
+          <t>#Python, #CodingTips, #FileManagement, #Programming</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>You can list the largest files in any directory using simple Python standard libraries. First, use os.walk to traverse the folder structure recursively. Then, calculate each file size using os.path.getsize. Store these values in a dictionary for easy sorting. Finally, sort the dictionary by size in descending order. This identifies the largest files without touching them. It is a safe way to audit disk usage. Subscribe for practical Python tips.</t>
+          <t>You can scan directories for empty folders using pure Python. Use os.walk to traverse directories safely. Check if the file list is empty. Print the path only when no files exist. This read-only approach prevents accidental deletion. It helps you identify redundant directories. You can then decide what to do next. Keep your file system organized effortlessly. No external libraries are required here. Just standard Python tools are needed. Stay safe and efficient with this method. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>You can list the largest files in any directory using simple Python standard libraries.</t>
+          <t>You can scan directories for empty folders using pure Python.</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -743,7 +743,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Python: Find Largest Files Safely</t>
+          <t>Python: List Empty Folders Safely</t>
         </is>
       </c>
       <c r="C3" t="n">

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-30T15:10:30.068107+00:00</t>
+          <t>2026-10-30T20:58:52.920511+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>41077536495</t>
+          <t>41126759004</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-30T15</t>
+          <t>2026-10-30T20</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/K5z__HAPHZk</t>
+          <t>https://youtube.com/shorts/zL7rBsuiRQg</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-30T15/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-30T20/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Python: List Empty Folders Safely</t>
+          <t>Timestamped Backups in 3 Lines</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>You can scan directories for empty folders using pure Python.</t>
+          <t>Stop worrying about overwriting files by adding timestamps to your backups.</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>The Mistake</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Python: List Empty Folders Safely</t>
+          <t>Timestamped Backups in 3 Lines</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to use Python's os.walk module to identify empty folders. This read-only technique ensures your data remains untouched while helping you organize your file system. Perfect for system maintenance and cleanup planning.</t>
+          <t>A quick tutorial on creating safe, timestamped file backups using Python's shutil and datetime libraries. Learn how to prevent accidental overwrites by generating unique filenames.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #CodingTips, #FileManagement, #Programming</t>
+          <t>#Python, #FileManagement, #CodingTips, #Scripting</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>You can scan directories for empty folders using pure Python. Use os.walk to traverse directories safely. Check if the file list is empty. Print the path only when no files exist. This read-only approach prevents accidental deletion. It helps you identify redundant directories. You can then decide what to do next. Keep your file system organized effortlessly. No external libraries are required here. Just standard Python tools are needed. Stay safe and efficient with this method. Subscribe for practical Python tips.</t>
+          <t>Stop worrying about overwriting files by adding timestamps to your backups. Learn how to create timestamped backup copies of any file using Python. Import shutil and datetime modules. Format the current date as a string. Define your source file path. Construct a new filename with the timestamp. Use shutil.copyfile to make the copy. This ensures your original remains untouched. The backup gets a unique name. Now you have a safe historical record. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>You can scan directories for empty folders using pure Python.</t>
+          <t>Stop worrying about overwriting files by adding timestamps to your backups.</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -730,7 +730,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>The Mistake</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -743,18 +743,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Python: List Empty Folders Safely</t>
+          <t>Timestamped Backups in 3 Lines</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>['no-number', 'no number, date or name - the most reliable single fix']</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-30T20:58:52.920511+00:00</t>
+          <t>2026-10-30T22:55:54.004679+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>41126759004</t>
+          <t>41140637410</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-30T20</t>
+          <t>2026-10-30T22</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/zL7rBsuiRQg</t>
+          <t>https://youtube.com/shorts/autT2j-_TVg</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-30T20/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-30T22/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Timestamped Backups in 3 Lines</t>
+          <t>Python: Find Duplicate Filenames Fast</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stop worrying about overwriting files by adding timestamps to your backups.</t>
+          <t>You can find duplicate filenames across folders using a simple Python dictionary.</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Mistake</t>
+          <t>Unclassified</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Timestamped Backups in 3 Lines</t>
+          <t>Python: Find Duplicate Filenames Fast</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A quick tutorial on creating safe, timestamped file backups using Python's shutil and datetime libraries. Learn how to prevent accidental overwrites by generating unique filenames.</t>
+          <t>Learn how to find duplicate filenames across folders using Python. This safe, read-only script uses os.walk and collections.Counter to identify repeated file names without modifying or deleting anything. Perfect for organizing large directories.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #FileManagement, #CodingTips, #Scripting</t>
+          <t>#Python, #CodingTips, #FileManagement, #Programming</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Stop worrying about overwriting files by adding timestamps to your backups. Learn how to create timestamped backup copies of any file using Python. Import shutil and datetime modules. Format the current date as a string. Define your source file path. Construct a new filename with the timestamp. Use shutil.copyfile to make the copy. This ensures your original remains untouched. The backup gets a unique name. Now you have a safe historical record. Subscribe for practical Python tips.</t>
+          <t>You can find duplicate filenames across folders using a simple Python dictionary. Import os and collections. Use os.walk to traverse directories. Store filenames in a Counter. Print names with counts greater than one. This helps you identify redundant files quickly. It is a safe read-only operation. You can extend this to check file sizes too. Always verify before taking any action. This technique works on any operating system. It keeps your file organization clean. Subscribe for more practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Stop worrying about overwriting files by adding timestamps to your backups.</t>
+          <t>You can find duplicate filenames across folders using a simple Python dictionary.</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -730,7 +730,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>The Mistake</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -743,14 +743,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Timestamped Backups in 3 Lines</t>
+          <t>Python: Find Duplicate Filenames Fast</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>['no-number', 'no number, date or name - the most reliable single fix']</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-30T22:55:54.004679+00:00</t>
+          <t>2026-10-31T01:18:29.115308+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>41140637410</t>
+          <t>41154249123</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-30T22</t>
+          <t>2026-10-31T01</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/autT2j-_TVg</t>
+          <t>https://youtube.com/shorts/_xMPed8fjdg</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-30T22/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-31T01/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Python: Find Duplicate Filenames Fast</t>
+          <t>Sort Downloads by Extension in Python</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>You can find duplicate filenames across folders using a simple Python dictionary.</t>
+          <t>Stop scrolling; here is how to preview file types in your downloads folder.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13">
@@ -578,7 +578,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>The Mistake</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Python: Find Duplicate Filenames Fast</t>
+          <t>Sort Downloads by Extension in Python</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to find duplicate filenames across folders using Python. This safe, read-only script uses os.walk and collections.Counter to identify repeated file names without modifying or deleting anything. Perfect for organizing large directories.</t>
+          <t>Learn how to preview file organization by extension in Python without modifying files.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #CodingTips, #FileManagement, #Programming</t>
+          <t>#Python, #Coding, #FileManagement, #Productivity</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>You can find duplicate filenames across folders using a simple Python dictionary. Import os and collections. Use os.walk to traverse directories. Store filenames in a Counter. Print names with counts greater than one. This helps you identify redundant files quickly. It is a safe read-only operation. You can extend this to check file sizes too. Always verify before taking any action. This technique works on any operating system. It keeps your file organization clean. Subscribe for more practical Python tips.</t>
+          <t>Stop scrolling; here is how to preview file types in your downloads folder. First, list all files in your directory. Extract the suffix for each file name. Add each file to a list under its specific extension key. Print the keys to see the categories. This preview mode ensures you never modify or move files. It is a safe way to visualize your data structure. You can then decide on a sorting strategy. This technique helps manage large folders efficiently. It keeps your workflow organized and predictable. Try it on a small test folder first. Always verify your path before running scripts. This approach saves time during cleanup. It reduces visual clutter in your file explorer. You gain insight into your file types. Use this method for any directory. It.</t>
         </is>
       </c>
     </row>
@@ -722,15 +722,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>You can find duplicate filenames across folders using a simple Python dictionary.</t>
+          <t>Stop scrolling; here is how to preview file types in your downloads folder.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>The Mistake</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -743,7 +743,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Python: Find Duplicate Filenames Fast</t>
+          <t>Sort Downloads by Extension in Python</t>
         </is>
       </c>
       <c r="C3" t="n">

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-31T01:18:29.115308+00:00</t>
+          <t>2026-10-31T03:01:08.661115+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>41154249123</t>
+          <t>41162260104</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-31T01</t>
+          <t>2026-10-31T02</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/_xMPed8fjdg</t>
+          <t>https://youtube.com/shorts/ClchcjxfFrE</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-31T01/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-31T02/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sort Downloads by Extension in Python</t>
+          <t>How to Find Empty Folders in Python</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stop scrolling; here is how to preview file types in your downloads folder.</t>
+          <t>Stop guessing which folders are useless; this script finds them safely.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sort Downloads by Extension in Python</t>
+          <t>How to Find Empty Folders in Python</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to preview file organization by extension in Python without modifying files.</t>
+          <t>Learn how to identify empty folders in Python using a safe, read-only approach. This script helps you find unused directories without risking data loss.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #Coding, #FileManagement, #Productivity</t>
+          <t>#Python, #CodingTips, #FileManagement, #Scripting</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Stop scrolling; here is how to preview file types in your downloads folder. First, list all files in your directory. Extract the suffix for each file name. Add each file to a list under its specific extension key. Print the keys to see the categories. This preview mode ensures you never modify or move files. It is a safe way to visualize your data structure. You can then decide on a sorting strategy. This technique helps manage large folders efficiently. It keeps your workflow organized and predictable. Try it on a small test folder first. Always verify your path before running scripts. This approach saves time during cleanup. It reduces visual clutter in your file explorer. You gain insight into your file types. Use this method for any directory. It.</t>
+          <t>Stop guessing which folders are useless; this script finds them safely. We use the os module to walk your directory tree. It checks if a folder has any subdirectories or files. If the list is empty, we print the path. This method only reads data. It never deletes or modifies anything. You get a clean list of targets. Then you can manually decide what to remove. This keeps your system organized and secure. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,11 +722,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Stop scrolling; here is how to preview file types in your downloads folder.</t>
+          <t>Stop guessing which folders are useless; this script finds them safely.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sort Downloads by Extension in Python</t>
+          <t>How to Find Empty Folders in Python</t>
         </is>
       </c>
       <c r="C3" t="n">

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-31T03:01:08.661115+00:00</t>
+          <t>2026-10-31T04:58:46.362154+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>41162260104</t>
+          <t>41170491420</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-31T02</t>
+          <t>2026-10-31T04</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/ClchcjxfFrE</t>
+          <t>https://youtube.com/shorts/gKUB1kV9M6Q</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-31T02/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-31T04/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>How to Find Empty Folders in Python</t>
+          <t>Python: Find Files Changed Today</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stop guessing which folders are useless; this script finds them safely.</t>
+          <t>You can find files changed today with a simple Python loop.</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Mistake</t>
+          <t>Unclassified</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>How to Find Empty Folders in Python</t>
+          <t>Python: Find Files Changed Today</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to identify empty folders in Python using a safe, read-only approach. This script helps you find unused directories without risking data loss.</t>
+          <t>Learn how to identify files modified today using Python's os module. This safe, read-only technique helps you track recent changes without modifying your data.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #CodingTips, #FileManagement, #Scripting</t>
+          <t>#Python, #Coding, #Programming, #FileManagement</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Stop guessing which folders are useless; this script finds them safely. We use the os module to walk your directory tree. It checks if a folder has any subdirectories or files. If the list is empty, we print the path. This method only reads data. It never deletes or modifies anything. You get a clean list of targets. Then you can manually decide what to remove. This keeps your system organized and secure. Subscribe for practical Python tips.</t>
+          <t>You can find files changed today with a simple Python loop. Start by importing the os library and time. Iterate through your directory with os.listdir. For each file, get its modification time using os.path.getmtime. Compare that timestamp to the current time minus eighty-six thousand four hundred seconds. If the difference is less than that, the file changed today. Print the filename to your console. This method is safe and read-only. It does not alter your data. Use this to track recent updates in your projects. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Stop guessing which folders are useless; this script finds them safely.</t>
+          <t>You can find files changed today with a simple Python loop.</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -730,7 +730,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>The Mistake</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -743,7 +743,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>How to Find Empty Folders in Python</t>
+          <t>Python: Find Files Changed Today</t>
         </is>
       </c>
       <c r="C3" t="n">

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-31T04:58:46.362154+00:00</t>
+          <t>2026-10-31T07:12:02.179994+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>41170491420</t>
+          <t>41179233287</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-31T04</t>
+          <t>2026-10-31T07</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/gKUB1kV9M6Q</t>
+          <t>https://youtube.com/shorts/4V6TtPyapI8</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-31T04/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-31T07/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Python: Find Files Changed Today</t>
+          <t>Secure Passwords: Python Local Method</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>You can find files changed today with a simple Python loop.</t>
+          <t>You can create secure, random passwords directly on your device using Python.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13">
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Python: Find Files Changed Today</t>
+          <t>Secure Passwords: Python Local Method</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to identify files modified today using Python's os module. This safe, read-only technique helps you track recent changes without modifying your data.</t>
+          <t>Learn how to generate strong, random passwords locally using Python's secrets module. This method ensures your data never leaves your device, providing maximum privacy and security against online threats. Perfect for developers and security-conscious users.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #Coding, #Programming, #FileManagement</t>
+          <t>#Python, #CyberSecurity, #Programming, #Privacy</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>You can find files changed today with a simple Python loop. Start by importing the os library and time. Iterate through your directory with os.listdir. For each file, get its modification time using os.path.getmtime. Compare that timestamp to the current time minus eighty-six thousand four hundred seconds. If the difference is less than that, the file changed today. Print the filename to your console. This method is safe and read-only. It does not alter your data. Use this to track recent updates in your projects. Subscribe for practical Python tips.</t>
+          <t>You can create secure, random passwords directly on your device using Python. Most online generators send your data to servers, but local scripts keep everything private. Use Python’s secrets module for true randomness. It draws from your operating system’s entropy pool, ensuring high security. Add letters, numbers, and symbols to create complex combinations. This method prevents dictionary attacks and brute-force attempts. You control the length and character set completely. No internet connection is required for this process. It is fast, safe, and fully transparent. You see exactly what characters are being used. This gives you total control over your digital security. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,11 +722,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>You can find files changed today with a simple Python loop.</t>
+          <t>You can create secure, random passwords directly on your device using Python.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Python: Find Files Changed Today</t>
+          <t>Secure Passwords: Python Local Method</t>
         </is>
       </c>
       <c r="C3" t="n">

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-31T07:12:02.179994+00:00</t>
+          <t>2026-10-31T08:58:48.956675+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>41179233287</t>
+          <t>41186448422</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-31T07</t>
+          <t>2026-10-31T08</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/4V6TtPyapI8</t>
+          <t>https://youtube.com/shorts/IP2aQAhQ6Xs</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-31T07/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-31T08/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Secure Passwords: Python Local Method</t>
+          <t>Python CSV: Print First 5 Rows</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>You can create secure, random passwords directly on your device using Python.</t>
+          <t>Need to peek at your CSV data quickly in Python?</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>The Question</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Secure Passwords: Python Local Method</t>
+          <t>Python CSV: Print First 5 Rows</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to generate strong, random passwords locally using Python's secrets module. This method ensures your data never leaves your device, providing maximum privacy and security against online threats. Perfect for developers and security-conscious users.</t>
+          <t>Learn how to read a CSV file and display the top five rows using Python and Pandas. This safe method allows you to preview your data structure without modifying the original file. Perfect for data exploration and debugging.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #CyberSecurity, #Programming, #Privacy</t>
+          <t>#Python, #Pandas, #DataScience, #CodingTips</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>You can create secure, random passwords directly on your device using Python. Most online generators send your data to servers, but local scripts keep everything private. Use Python’s secrets module for true randomness. It draws from your operating system’s entropy pool, ensuring high security. Add letters, numbers, and symbols to create complex combinations. This method prevents dictionary attacks and brute-force attempts. You control the length and character set completely. No internet connection is required for this process. It is fast, safe, and fully transparent. You see exactly what characters are being used. This gives you total control over your digital security. Subscribe for practical Python tips.</t>
+          <t>Need to peek at your CSV data quickly in Python? Stop scrolling through huge files manually. Instead, use Pandas to load and inspect your data. Import the library, then read your CSV file into a DataFrame. The head method displays the first five rows by default. This lets you verify columns and data types instantly. It is safe, fast, and requires no file modification. You can also adjust the row count if needed. Master this simple technique to debug data quickly. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>You can create secure, random passwords directly on your device using Python.</t>
+          <t>Need to peek at your CSV data quickly in Python?</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -730,7 +730,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>The Question</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -743,18 +743,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Secure Passwords: Python Local Method</t>
+          <t>Python CSV: Print First 5 Rows</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>['no-number', 'no number, date or name - the most reliable single fix']</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-31T08:58:48.956675+00:00</t>
+          <t>2026-10-31T10:53:05.169855+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>41186448422</t>
+          <t>41194172410</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-31T08</t>
+          <t>2026-10-31T10</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/IP2aQAhQ6Xs</t>
+          <t>https://youtube.com/shorts/_fX5xYg9re0</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-31T08/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-31T10/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Python CSV: Print First 5 Rows</t>
+          <t>Count File Types in Python</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Need to peek at your CSV data quickly in Python?</t>
+          <t>Learn how to tally file extensions using standard Python tools.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
@@ -578,7 +578,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Question</t>
+          <t>Unclassified</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Python CSV: Print First 5 Rows</t>
+          <t>Count File Types in Python</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to read a CSV file and display the top five rows using Python and Pandas. This safe method allows you to preview your data structure without modifying the original file. Perfect for data exploration and debugging.</t>
+          <t>Learn how to count file types in a folder using Python's pathlib module. This script safely reads directory contents and tallies extensions without modifying any files. Perfect for quick data analysis tasks.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #Pandas, #DataScience, #CodingTips</t>
+          <t>#python, #coding, #productivity, #scripting</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Need to peek at your CSV data quickly in Python? Stop scrolling through huge files manually. Instead, use Pandas to load and inspect your data. Import the library, then read your CSV file into a DataFrame. The head method displays the first five rows by default. This lets you verify columns and data types instantly. It is safe, fast, and requires no file modification. You can also adjust the row count if needed. Master this simple technique to debug data quickly. Subscribe for practical Python tips.</t>
+          <t>Learn how to tally file extensions using standard Python tools. First, import the pathlib module to handle file paths safely. Create a list of all files in the target directory. Use a dictionary to store counts for each file extension. Iterate through the files and update the count for each unique extension. Print the results to see the breakdown. This method is efficient and requires no third-party packages. It works on any operating system. Now you can analyze folder contents easily. Subscribe for more practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,15 +722,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Need to peek at your CSV data quickly in Python?</t>
+          <t>Learn how to tally file extensions using standard Python tools.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>The Question</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -743,14 +743,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Python CSV: Print First 5 Rows</t>
+          <t>Count File Types in Python</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>['no-number', 'no number, date or name - the most reliable single fix']</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-31T10:53:05.169855+00:00</t>
+          <t>2026-10-31T13:04:59.868638+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>41194172410</t>
+          <t>41203522854</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-31T10</t>
+          <t>2026-10-31T13</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/_fX5xYg9re0</t>
+          <t>https://youtube.com/shorts/38rFvIhAc1k</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-31T10/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-31T13/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Count File Types in Python</t>
+          <t>Python shutil.copy2 Explained</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Learn how to tally file extensions using standard Python tools.</t>
+          <t>Stop losing data by making timestamped copies in Python.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13">
@@ -578,7 +578,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>The Mistake</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Count File Types in Python</t>
+          <t>Python shutil.copy2 Explained</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to count file types in a folder using Python's pathlib module. This script safely reads directory contents and tallies extensions without modifying any files. Perfect for quick data analysis tasks.</t>
+          <t>Learn how to create a safe, timestamped backup of a single file using Python's shutil module. This technique ensures your original data remains untouched while creating a verified copy with a date stamp. Perfect for developers and data enthusiasts looking to implement basic file safety routines.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#python, #coding, #productivity, #scripting</t>
+          <t>#Python, #FileManagement, #CodingTips, #DataSafety</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Learn how to tally file extensions using standard Python tools. First, import the pathlib module to handle file paths safely. Create a list of all files in the target directory. Use a dictionary to store counts for each file extension. Iterate through the files and update the count for each unique extension. Print the results to see the breakdown. This method is efficient and requires no third-party packages. It works on any operating system. Now you can analyze folder contents easily. Subscribe for more practical Python tips.</t>
+          <t>Stop losing data by making timestamped copies in Python. Never risk overwriting your original data. Use the shutil module and the copy2 function. It preserves metadata, ensuring the backup is exact. Add a timestamp to the filename. This creates a unique, dated copy. You can then verify the new file exists. This method is safe and simple. It prevents accidental losses. Always keep your originals intact. This is a reliable habit. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,15 +722,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Learn how to tally file extensions using standard Python tools.</t>
+          <t>Stop losing data by making timestamped copies in Python.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>The Mistake</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -743,18 +743,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Count File Types in Python</t>
+          <t>Python shutil.copy2 Explained</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>['no-number', 'no number, date or name - the most reliable single fix']</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/latest/amala-operations.xlsx
+++ b/reports/latest/amala-operations.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-31T13:04:59.868638+00:00</t>
+          <t>2026-10-31T14:52:34.689456+00:00</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>41203522854</t>
+          <t>41211728719</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-31T13</t>
+          <t>2026-10-31T14</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/38rFvIhAc1k</t>
+          <t>https://youtube.com/shorts/3H2z4ac1FAU</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-31T13/amala-short.mp4</t>
+          <t>/home/runner/work/automated-YT-operations/automated-YT-operations/hourly-output/2026-10-31T14/amala-short.mp4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Python shutil.copy2 Explained</t>
+          <t>Check File Modification Times in Python</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stop losing data by making timestamped copies in Python.</t>
+          <t>Stop guessing which files changed today in your directory.</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13">
@@ -628,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Python shutil.copy2 Explained</t>
+          <t>Check File Modification Times in Python</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Learn how to create a safe, timestamped backup of a single file using Python's shutil module. This technique ensures your original data remains untouched while creating a verified copy with a date stamp. Perfect for developers and data enthusiasts looking to implement basic file safety routines.</t>
+          <t>Learn how to find files changed today using Python's os module. This safe script only reads metadata and never modifies your data.</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#Python, #FileManagement, #CodingTips, #DataSafety</t>
+          <t>#python, #coding, #productivity, #scripting</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Stop losing data by making timestamped copies in Python. Never risk overwriting your original data. Use the shutil module and the copy2 function. It preserves metadata, ensuring the backup is exact. Add a timestamp to the filename. This creates a unique, dated copy. You can then verify the new file exists. This method is safe and simple. It prevents accidental losses. Always keep your originals intact. This is a reliable habit. Subscribe for practical Python tips.</t>
+          <t>Stop guessing which files changed today in your directory. Python has a built-in way to check file modification times. You can find files changed today without external libraries. The os module makes checking file timestamps very simple. Here is how to list files modified today safely in Python. We use os.path.getmtime to get the last modified time. Then we compare it to the current date. This script only reads file metadata. It never modifies or deletes anything. It is a safe and fast method. Subscribe for practical Python tips.</t>
         </is>
       </c>
     </row>
@@ -722,11 +722,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Stop losing data by making timestamped copies in Python.</t>
+          <t>Stop guessing which files changed today in your directory.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -743,14 +743,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Python shutil.copy2 Explained</t>
+          <t>Check File Modification Times in Python</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>['no-number', 'no number, date or name - the most reliable single fix']</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
